--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211336135864</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
@@ -65,43 +65,43 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734416007996</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419034004211</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95420968532562</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162525177002</t>
@@ -287,31 +287,31 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,31 +335,31 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420682907104</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537700653076</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.21358942985535</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.77987670898438</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.4274697303772</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -66390,7 +66390,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.5871527778</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>2100</v>
@@ -66411,6 +66411,32 @@
         <v>467</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6362962963</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211336135864</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630555152893</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734416007996</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268941879272</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -140,37 +140,37 @@
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664690971375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -194,40 +194,40 @@
     <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420968532562</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153100013733</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087135314941</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358942985535</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218029022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987694740295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -66416,7 +66416,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6362962963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>4500</v>
@@ -66437,6 +66437,32 @@
         <v>465</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.4083101852</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>466</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053621292114</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472840309143</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.867356300354</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331464767456</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -365,25 +365,25 @@
     <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,22 +458,22 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588753700256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -1420,6 +1420,9 @@
   <si>
     <t xml:space="preserve">1.37999999523163</t>
   </si>
+  <si>
+    <t xml:space="preserve">1.32000005245209</t>
+  </si>
 </sst>
 </file>
 
@@ -66469,6 +66472,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.2916666667</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>467</v>
+      </c>
+      <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6099305556</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -62,52 +62,52 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693359375</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415934562683</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242270469666</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382910728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537700653076</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588753700256</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -689,43 +689,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1019,31 +1019,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -66500,7 +66500,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6099305556</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>4200</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429738044739</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429834365845</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129977226257</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303093910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373735427856</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124955177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
     <t xml:space="preserve">3.46546578407288</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -66602,6 +66602,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.2916666667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.5711226852</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="471">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,67 +44,67 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422857284546</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630555152893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688232421875</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429738044739</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -179,46 +179,46 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -377,49 +377,49 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
     <t xml:space="preserve">3.7433979511261</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -1422,6 +1422,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.35000002384186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37000000476837</t>
   </si>
 </sst>
 </file>
@@ -66630,7 +66633,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.5711226852</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>600</v>
@@ -66651,6 +66654,32 @@
         <v>469</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.422662037</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664690971375</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242270469666</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,37 +362,37 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537724494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.4274697303772</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -66738,6 +66738,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.3333333333</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>471</v>
+      </c>
+      <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.3660416667</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.1782054901123</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
@@ -155,31 +155,31 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134404182434</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237819671631</t>
+    <t xml:space="preserve">2.03237843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519671440125</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941842079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096013069153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -66841,7 +66841,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.4363310185</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>3600</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945937156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0552282333374</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.46664690971375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139450073242</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -245,22 +245,22 @@
     <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087480545044</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -305,31 +305,31 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373759269714</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124979019165</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091586112976</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218029022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,64 +458,64 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870058059692</t>
+    <t xml:space="preserve">4.03870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2503719329834</t>
+    <t xml:space="preserve">4.25037145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1547384262085</t>
+    <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246206283569</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350065231323</t>
+    <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
     <t xml:space="preserve">4.10160827636719</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881357192993</t>
+    <t xml:space="preserve">4.30881404876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661642074585</t>
+    <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -713,31 +713,31 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846422195435</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1019,31 +1019,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -53,19 +53,19 @@
     <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157482147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085947990417</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -242,25 +242,25 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020742416382</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -464,22 +464,22 @@
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -66943,6 +66943,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.3333333333</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6813078704</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157482147217</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
@@ -170,52 +170,52 @@
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134404182434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519671440125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050220012665</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800928115845</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331512451172</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -440,22 +440,22 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5610044002533</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4758882522583</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -66971,7 +66971,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6813078704</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>2100</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315125465393</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693359375</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.76139450073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824526786804</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669463157654</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110829353333</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373759269714</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542675018311</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115553855896</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.692467212677</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706687927246</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194727897644</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964548110962</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072390556335</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649970054626</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339771270752</t>
@@ -67047,6 +67047,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.3333333333</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368955612183</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421016216278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -263,25 +263,25 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420682907104</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987599372864</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -67125,6 +67125,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.3333333333</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945937156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -191,70 +191,70 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421016216278</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -329,31 +329,31 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382910728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -380,61 +380,61 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34386992454529</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987599372864</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67151,6 +67151,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.3333333333</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6562268518</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,52 +59,52 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630555152893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945937156677</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688232421875</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,34 +143,34 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -179,31 +179,31 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
@@ -212,55 +212,55 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115553855896</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382910728455</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020694732666</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -419,73 +419,73 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964548110962</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67179,7 +67179,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6562268518</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>300</v>
@@ -67200,6 +67200,32 @@
         <v>470</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.485625</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,49 +44,49 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22368955612183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157410621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401329994202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688232421875</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053621292114</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998571872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693347454071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138902664185</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955694198608</t>
@@ -371,55 +371,55 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194727897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
@@ -461,43 +461,43 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67205,7 +67205,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.485625</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>300</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368955612183</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">2.18157410621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.0552282333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401329994202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053621292114</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472840309143</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -167,52 +167,52 @@
     <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237819671631</t>
+    <t xml:space="preserve">2.03237843513489</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735606193542</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998571872711</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693347454071</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669463157654</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091586112976</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194727897644</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.7017080783844</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -67229,6 +67229,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.3333333333</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745167732239</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007437705994</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373759269714</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594418525696</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884802818298</t>
+    <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415089607239</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.77987623214722</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -67309,7 +67309,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.3760069444</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>600</v>
@@ -67330,6 +67330,32 @@
         <v>441</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.4717013889</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522847175598</t>
@@ -86,19 +86,19 @@
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11418962478638</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820501327515</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -197,31 +197,31 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139450073242</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824526786804</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373759269714</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,16 +494,16 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2503719329834</t>
+    <t xml:space="preserve">4.25037145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1547384262085</t>
+    <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
     <t xml:space="preserve">4.28579092025757</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246206283569</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -545,52 +545,52 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350065231323</t>
+    <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881357192993</t>
+    <t xml:space="preserve">4.30881404876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661642074585</t>
+    <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754703521729</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846422195435</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67335,7 +67335,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.4717013889</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>4500</v>
@@ -67356,6 +67356,32 @@
         <v>470</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.605150463</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945913314819</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418962478638</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237819671631</t>
+    <t xml:space="preserve">2.03237843513489</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050220012665</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941842079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800928115845</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331512451172</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -311,25 +311,25 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096013069153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5610044002533</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4758882522583</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
@@ -470,31 +470,31 @@
     <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296745300293</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693605422974</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
     <t xml:space="preserve">4.03785228729248</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754703521729</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67361,7 +67361,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.605150463</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>2100</v>
@@ -67382,6 +67382,32 @@
         <v>470</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.4053587963</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>900</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11419034004211</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791776657104</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941842079163</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162525177002</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.32420682907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096013069153</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67387,7 +67387,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.4053587963</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>900</v>
@@ -67408,6 +67408,32 @@
         <v>470</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.5914699074</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
@@ -116,43 +116,43 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735606193542</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683934211731</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669463157654</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -323,43 +323,43 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
@@ -392,34 +392,34 @@
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
@@ -440,46 +440,46 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67463,6 +67463,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,43 +59,43 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.0552282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,34 +143,34 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -179,70 +179,70 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138902664185</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303093910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -284,28 +284,28 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026335716248</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124955177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -377,34 +377,34 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67595,7 +67595,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.5168402778</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>1500</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945913314819</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0552282333374</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44269013404846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,73 +194,73 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,58 +269,58 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,31 +377,31 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67619,6 +67619,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.3333333333</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,46 +62,46 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429738044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44269013404846</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519647598267</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050220012665</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800928115845</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331512451172</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166952133179</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772533416748</t>
@@ -374,28 +374,28 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020742416382</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5610044002533</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4758882522583</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67645,6 +67645,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -104,55 +104,55 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796155929565</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.18871521949768</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420968532562</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.76139450073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.30857348442078</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153100013733</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087135314941</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -368,46 +368,46 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358942985535</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884826660156</t>
+    <t xml:space="preserve">3.17884802818298</t>
   </si>
   <si>
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,34 +485,34 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25037145614624</t>
+    <t xml:space="preserve">4.2503719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15473794937134</t>
+    <t xml:space="preserve">4.1547384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246206283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350112915039</t>
+    <t xml:space="preserve">4.30350065231323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
     <t xml:space="preserve">4.10160827636719</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881404876709</t>
+    <t xml:space="preserve">4.30881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661594390869</t>
+    <t xml:space="preserve">4.18661642074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,31 +710,31 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67725,7 +67725,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.3334722222</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>300</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,49 +62,49 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.0552282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401329994202</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745167732239</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -164,22 +164,22 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735606193542</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139450073242</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824526786804</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190550804138</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537676811218</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -422,31 +422,31 @@
     <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884802818298</t>
+    <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218029022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762489318848</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870058059692</t>
+    <t xml:space="preserve">4.03870010375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2503719329834</t>
+    <t xml:space="preserve">4.25037145614624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1547384262085</t>
+    <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
     <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246206283569</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350065231323</t>
+    <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881357192993</t>
+    <t xml:space="preserve">4.30881404876709</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661642074585</t>
+    <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.33892107009888</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.98472309112549</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107412338257</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434005737305</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846422195435</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -67749,6 +67749,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.3333333333</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
@@ -62,55 +62,55 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0552282333374</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401329994202</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419034004211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735606193542</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,58 +272,58 @@
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420682907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603593826294</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -389,64 +389,64 @@
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,49 +455,49 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762489318848</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870010375977</t>
+    <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157482147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419034004211</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.44268989562988</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791776657104</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420682907104</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603593826294</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945937156677</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429834365845</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265916824341</t>
@@ -197,52 +197,52 @@
     <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -302,49 +302,49 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115553855896</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382910728455</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.692467212677</t>
@@ -368,40 +368,40 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
@@ -410,37 +410,37 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884826660156</t>
+    <t xml:space="preserve">3.17884802818298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964548110962</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072438240051</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -461,22 +461,22 @@
     <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25037145614624</t>
+    <t xml:space="preserve">4.2503719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15473794937134</t>
+    <t xml:space="preserve">4.1547384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246206283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350112915039</t>
+    <t xml:space="preserve">4.30350065231323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
     <t xml:space="preserve">4.10160827636719</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881404876709</t>
+    <t xml:space="preserve">4.30881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661594390869</t>
+    <t xml:space="preserve">4.18661642074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -67907,7 +67907,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.6791898148</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>900</v>
@@ -67928,6 +67928,32 @@
         <v>468</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.4995138889</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>466</v>
+      </c>
+      <c r="H2546" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211264610291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,64 +152,64 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.86735606193542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420968532562</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988813400269</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153100013733</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,52 +335,52 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087135314941</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -389,52 +389,52 @@
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358942985535</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218029022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762489318848</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870058059692</t>
+    <t xml:space="preserve">4.03870010375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -67985,7 +67985,7 @@
     </row>
     <row r="2548">
       <c r="A2548" s="1" t="n">
-        <v>46034.4463541667</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B2548" t="n">
         <v>1500</v>
@@ -67997,7 +67997,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="E2548" t="n">
-        <v>1.3400000333786</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="F2548" t="n">
         <v>1.32000005245209</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211264610291</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945937156677</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -164,22 +164,22 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735606193542</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -221,37 +221,37 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,67 +302,67 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382910728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016267776489</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762489318848</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870010375977</t>
+    <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -68009,6 +68009,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2549">
+      <c r="A2549" s="1" t="n">
+        <v>46035.3333333333</v>
+      </c>
+      <c r="B2549" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2549" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2549" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2549" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F2549" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2549" t="s">
+        <v>468</v>
+      </c>
+      <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745191574097</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576725006104</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735606193542</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444614887238</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -242,37 +242,37 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
@@ -350,43 +350,43 @@
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537724494934</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -428,79 +428,79 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762489318848</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.77987694740295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03870010375977</t>
+    <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,58 +686,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1019,31 +1019,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68173,7 +68173,7 @@
     </row>
     <row r="2555">
       <c r="A2555" s="1" t="n">
-        <v>46043.4815509259</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B2555" t="n">
         <v>1500</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.22874331474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418962478638</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576725006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542099237442</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444614887238</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -281,37 +281,37 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
@@ -350,52 +350,52 @@
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -68197,6 +68197,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2556">
+      <c r="A2556" s="1" t="n">
+        <v>46044.3333333333</v>
+      </c>
+      <c r="B2556" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2556" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2556" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2556" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.5767592593</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2557" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11419034004211</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026335716248</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.32420682907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -362,49 +362,49 @@
     <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668296813965</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -68251,7 +68251,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.458912037</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>2100</v>
@@ -68272,6 +68272,32 @@
         <v>472</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.6114583333</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419034004211</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420682907104</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -386,34 +386,34 @@
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
     <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668296813965</t>
@@ -68277,7 +68277,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6114583333</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>10800</v>
@@ -68298,6 +68298,32 @@
         <v>441</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6456018519</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945913314819</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053621292114</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576725006104</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.867356300354</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331464767456</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -365,25 +365,25 @@
     <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -458,22 +458,22 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588753700256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -68332,7 +68332,7 @@
     </row>
     <row r="2561">
       <c r="A2561" s="1" t="n">
-        <v>46051.3732523148</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2561" t="n">
         <v>600</v>
@@ -68353,6 +68353,32 @@
         <v>471</v>
       </c>
       <c r="H2561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="1" t="n">
+        <v>46052.3408449074</v>
+      </c>
+      <c r="B2562" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2562" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2562" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2562" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>471</v>
+      </c>
+      <c r="H2562" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796155929565</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95420968532562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129977226257</t>
@@ -209,79 +209,79 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.21358942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067670822144</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.2680811882019</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68431,6 +68431,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2565">
+      <c r="A2565" s="1" t="n">
+        <v>46057.3333333333</v>
+      </c>
+      <c r="B2565" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2565" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2565" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2565" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,58 +62,58 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796155929565</t>
@@ -161,64 +161,64 @@
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420968532562</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998571872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693347454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -263,37 +263,37 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.30857348442078</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153100013733</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087135314941</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -368,46 +368,46 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358942985535</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194727897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68457,6 +68457,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.3333333333</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2566" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.22874331474304</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
@@ -80,55 +80,55 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -158,43 +158,43 @@
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134404182434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519671440125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998571872711</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693347454071</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
@@ -299,49 +299,49 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194727897644</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -449,43 +449,43 @@
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68483,6 +68483,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2567">
+      <c r="A2567" s="1" t="n">
+        <v>46059.3333333333</v>
+      </c>
+      <c r="B2567" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2567" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D2567" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E2567" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.3333912037</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>468</v>
+      </c>
+      <c r="H2568" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.27085947990417</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134404182434</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519671440125</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124979019165</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,43 +362,43 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335022926331</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067670822144</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
     <t xml:space="preserve">4.2680811882019</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68511,7 +68511,7 @@
     </row>
     <row r="2568">
       <c r="A2568" s="1" t="n">
-        <v>46062.3333912037</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2568" t="n">
         <v>1200</v>
@@ -68532,6 +68532,32 @@
         <v>468</v>
       </c>
       <c r="H2568" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" s="1" t="n">
+        <v>46063.3951851852</v>
+      </c>
+      <c r="B2569" t="n">
+        <v>900</v>
+      </c>
+      <c r="C2569" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D2569" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E2569" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F2569" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>472</v>
+      </c>
+      <c r="H2569" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945913314819</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401282310486</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085947990417</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134404182434</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519671440125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.25124979019165</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,43 +362,43 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335022926331</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067670822144</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.2680811882019</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68537,7 +68537,7 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46063.3951851852</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2569" t="n">
         <v>900</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211264610291</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -149,67 +149,67 @@
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420968532562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -245,52 +245,52 @@
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988813400269</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087135314941</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
@@ -383,70 +383,70 @@
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.21358942985535</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,40 +455,40 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -68615,7 +68615,7 @@
     </row>
     <row r="2572">
       <c r="A2572" s="1" t="n">
-        <v>46066.6759722222</v>
+        <v>46066.3333333333</v>
       </c>
       <c r="B2572" t="n">
         <v>2700</v>
@@ -68636,6 +68636,32 @@
         <v>472</v>
       </c>
       <c r="H2572" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" s="1" t="n">
+        <v>46069.4066203704</v>
+      </c>
+      <c r="B2573" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2573" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="D2573" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E2573" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="F2573" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="G2573" t="s">
+        <v>471</v>
+      </c>
+      <c r="H2573" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422857284546</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -137,70 +137,70 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664690971375</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998571872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693347454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
@@ -239,55 +239,55 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
@@ -299,55 +299,55 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -356,40 +356,40 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194727897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,37 +455,37 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -1434,6 +1434,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.29999995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28999996185303</t>
   </si>
 </sst>
 </file>
@@ -68696,7 +68699,7 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46071.3334027778</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2575" t="n">
         <v>300</v>
@@ -68717,6 +68720,32 @@
         <v>468</v>
       </c>
       <c r="H2575" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46072.6862615741</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>474</v>
+      </c>
+      <c r="H2576" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.22874331474304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788198471069</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -158,43 +158,43 @@
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134404182434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.95420980453491</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519671440125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998571872711</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693347454071</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
@@ -299,49 +299,49 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
@@ -356,70 +356,70 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194727897644</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -449,43 +449,43 @@
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327270507812</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68725,7 +68725,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.6862615741</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>300</v>
@@ -68746,6 +68746,32 @@
         <v>474</v>
       </c>
       <c r="H2576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.5767013889</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>472</v>
+      </c>
+      <c r="H2577" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211264610291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522847175598</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.3971643447876</t>
@@ -164,52 +164,52 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134404182434</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519671440125</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,46 +272,46 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
@@ -323,25 +323,25 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,70 +362,70 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -434,46 +434,46 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -68803,7 +68803,7 @@
     </row>
     <row r="2579">
       <c r="A2579" s="1" t="n">
-        <v>46077.6455555556</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2579" t="n">
         <v>18000</v>
@@ -68824,6 +68824,32 @@
         <v>465</v>
       </c>
       <c r="H2579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" s="1" t="n">
+        <v>46078.685</v>
+      </c>
+      <c r="B2580" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C2580" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2580" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E2580" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F2580" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2580" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211264610291</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429738044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788246154785</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,40 +146,40 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
@@ -233,37 +233,37 @@
     <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303093910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124955177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,37 +362,37 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016267776489</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68829,7 +68829,7 @@
     </row>
     <row r="2580">
       <c r="A2580" s="1" t="n">
-        <v>46078.685</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2580" t="n">
         <v>8400</v>
@@ -68850,6 +68850,32 @@
         <v>469</v>
       </c>
       <c r="H2580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46079.6341550926</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>470</v>
+      </c>
+      <c r="H2581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -50,22 +50,22 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945937156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.27085947990417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421016216278</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303093910217</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124955177307</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,49 +377,49 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,25 +431,25 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987599372864</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -68959,7 +68959,7 @@
     </row>
     <row r="2585">
       <c r="A2585" s="1" t="n">
-        <v>46085.6356712963</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B2585" t="n">
         <v>8400</v>
@@ -68980,6 +68980,32 @@
         <v>471</v>
       </c>
       <c r="H2585" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" s="1" t="n">
+        <v>46086.6435069444</v>
+      </c>
+      <c r="B2586" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C2586" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D2586" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E2586" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F2586" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G2586" t="s">
+        <v>468</v>
+      </c>
+      <c r="H2586" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,37 +50,37 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
@@ -92,58 +92,58 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085947990417</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.76139450073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.21824526786804</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373735427856</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.692467212677</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17884826660156</t>
+    <t xml:space="preserve">3.17884802818298</t>
   </si>
   <si>
     <t xml:space="preserve">3.2396457195282</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
     <t xml:space="preserve">3.58706092834473</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25037145614624</t>
+    <t xml:space="preserve">4.2503719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15473794937134</t>
+    <t xml:space="preserve">4.1547384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246206283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350112915039</t>
+    <t xml:space="preserve">4.30350065231323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
     <t xml:space="preserve">4.10160827636719</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881404876709</t>
+    <t xml:space="preserve">4.30881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661594390869</t>
+    <t xml:space="preserve">4.18661642074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -69037,7 +69037,7 @@
     </row>
     <row r="2588">
       <c r="A2588" s="1" t="n">
-        <v>46090.6191203704</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B2588" t="n">
         <v>20100</v>
@@ -69058,6 +69058,32 @@
         <v>438</v>
       </c>
       <c r="H2588" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" s="1" t="n">
+        <v>46091.672662037</v>
+      </c>
+      <c r="B2589" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C2589" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2589" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2589" t="n">
+        <v>1.47000002861023</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>436</v>
+      </c>
+      <c r="H2589" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157410621643</t>
+    <t xml:space="preserve">2.18157482147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0552282333374</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401329994202</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429738044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472840309143</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
     <t xml:space="preserve">2.17134428024292</t>
@@ -179,40 +179,40 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735606193542</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -221,37 +221,37 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669463157654</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542675018311</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382910728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -434,49 +434,49 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -69115,7 +69115,7 @@
     </row>
     <row r="2591">
       <c r="A2591" s="1" t="n">
-        <v>46093.6233680556</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2591" t="n">
         <v>900</v>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="476">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422857284546</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157482147217</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429738044739</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831276893616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576677322388</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,55 +194,55 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,46 +281,46 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115553855896</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382910728455</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964548110962</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -1437,6 +1437,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.28999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -69139,6 +69142,82 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2592" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="G2592" t="s">
+        <v>443</v>
+      </c>
+      <c r="H2592" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46097.3333333333</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2593"/>
+      <c r="G2593" t="s">
+        <v>475</v>
+      </c>
+      <c r="H2593" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46097.6766087963</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F2594" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G2594" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945937156677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157482147217</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315149307251</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831276893616</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576677322388</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
@@ -194,55 +194,55 @@
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
     <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050220012665</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800928115845</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,46 +281,46 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331512451172</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382910728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5610044002533</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4758882522583</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69184,9 +69184,11 @@
       <c r="E2593" t="n">
         <v>1.39999997615814</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>1.39999997615814</v>
+      </c>
       <c r="G2593" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="H2593" t="s">
         <v>9</v>
@@ -69194,27 +69196,51 @@
     </row>
     <row r="2594">
       <c r="A2594" s="1" t="n">
-        <v>46097.6766087963</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2594" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="C2594" t="n">
-        <v>1.39999997615814</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="D2594" t="n">
-        <v>1.39999997615814</v>
+        <v>1.42999994754791</v>
       </c>
       <c r="E2594" t="n">
-        <v>1.39999997615814</v>
-      </c>
-      <c r="F2594" t="n">
-        <v>1.39999997615814</v>
-      </c>
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2594"/>
       <c r="G2594" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46098.6698842593</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>1.42999994754791</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2595" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -56,43 +56,43 @@
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945937156677</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576677322388</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.1782054901123</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875972747803</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.17134404182434</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -185,46 +185,46 @@
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519671440125</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941794395447</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115553855896</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382910728455</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
     <t xml:space="preserve">3.23096036911011</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964548110962</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
@@ -449,52 +449,52 @@
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,22 +587,22 @@
     <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067670822144</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40976047515869</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.2680811882019</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69210,9 +69210,11 @@
       <c r="E2594" t="n">
         <v>1.42999994754791</v>
       </c>
-      <c r="F2594"/>
+      <c r="F2594" t="n">
+        <v>1.46000003814697</v>
+      </c>
       <c r="G2594" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="H2594" t="s">
         <v>9</v>
@@ -69220,27 +69222,51 @@
     </row>
     <row r="2595">
       <c r="A2595" s="1" t="n">
-        <v>46098.6698842593</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B2595" t="n">
-        <v>1500</v>
+        <v>9900</v>
       </c>
       <c r="C2595" t="n">
-        <v>1.46000003814697</v>
+        <v>1.50999999046326</v>
       </c>
       <c r="D2595" t="n">
-        <v>1.42999994754791</v>
+        <v>1.48000001907349</v>
       </c>
       <c r="E2595" t="n">
-        <v>1.42999994754791</v>
-      </c>
-      <c r="F2595" t="n">
-        <v>1.46000003814697</v>
-      </c>
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F2595"/>
       <c r="G2595" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="H2595" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46099.5763194444</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>433</v>
+      </c>
+      <c r="H2596" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261271476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -86,40 +86,40 @@
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
     <t xml:space="preserve">2.2708592414856</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429834365845</t>
@@ -155,64 +155,64 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -224,40 +224,40 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415958404541</t>
+    <t xml:space="preserve">2.36415934562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941842079163</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303093910217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25124955177307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096013069153</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -69288,9 +69288,11 @@
       <c r="E2597" t="n">
         <v>1.44000005722046</v>
       </c>
-      <c r="F2597"/>
+      <c r="F2597" t="n">
+        <v>1.44000005722046</v>
+      </c>
       <c r="G2597" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="H2597" t="s">
         <v>9</v>
@@ -69298,27 +69300,51 @@
     </row>
     <row r="2598">
       <c r="A2598" s="1" t="n">
-        <v>46101.6711111111</v>
+        <v>46104.3333333333</v>
       </c>
       <c r="B2598" t="n">
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="C2598" t="n">
-        <v>1.44000005722046</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="D2598" t="n">
-        <v>1.44000005722046</v>
+        <v>1.4099999666214</v>
       </c>
       <c r="E2598" t="n">
-        <v>1.44000005722046</v>
-      </c>
-      <c r="F2598" t="n">
-        <v>1.44000005722046</v>
-      </c>
+        <v>1.4099999666214</v>
+      </c>
+      <c r="F2598"/>
       <c r="G2598" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="H2598" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" s="1" t="n">
+        <v>46104.578275463</v>
+      </c>
+      <c r="B2599" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2599" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="E2599" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2599" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2599" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261271476746</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -83,34 +83,34 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745167732239</t>
+    <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429834365845</t>
@@ -155,64 +155,64 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871474266052</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237819671631</t>
+    <t xml:space="preserve">2.03237843513489</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -224,40 +224,40 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36415934562683</t>
+    <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941842079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.3085732460022</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096013069153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668272972107</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
     <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -69314,9 +69314,11 @@
       <c r="E2598" t="n">
         <v>1.4099999666214</v>
       </c>
-      <c r="F2598"/>
+      <c r="F2598" t="n">
+        <v>1.4099999666214</v>
+      </c>
       <c r="G2598" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="H2598" t="s">
         <v>9</v>
@@ -69324,27 +69326,51 @@
     </row>
     <row r="2599">
       <c r="A2599" s="1" t="n">
-        <v>46104.578275463</v>
+        <v>46105.3333333333</v>
       </c>
       <c r="B2599" t="n">
-        <v>2100</v>
+        <v>13800</v>
       </c>
       <c r="C2599" t="n">
-        <v>1.4099999666214</v>
+        <v>1.38999998569489</v>
       </c>
       <c r="D2599" t="n">
-        <v>1.4099999666214</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="E2599" t="n">
-        <v>1.4099999666214</v>
-      </c>
-      <c r="F2599" t="n">
-        <v>1.4099999666214</v>
-      </c>
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2599"/>
       <c r="G2599" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="H2599" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="1" t="n">
+        <v>46105.6334722222</v>
+      </c>
+      <c r="B2600" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C2600" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="D2600" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E2600" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="G2600" t="s">
+        <v>464</v>
+      </c>
+      <c r="H2600" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,34 +233,34 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941842079163</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,28 +338,28 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096013069153</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -443,43 +443,43 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69340,9 +69340,11 @@
       <c r="E2599" t="n">
         <v>1.37999999523163</v>
       </c>
-      <c r="F2599"/>
+      <c r="F2599" t="n">
+        <v>1.38999998569489</v>
+      </c>
       <c r="G2599" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="H2599" t="s">
         <v>9</v>
@@ -69350,27 +69352,51 @@
     </row>
     <row r="2600">
       <c r="A2600" s="1" t="n">
-        <v>46105.6334722222</v>
+        <v>46106.3333333333</v>
       </c>
       <c r="B2600" t="n">
-        <v>13800</v>
+        <v>600</v>
       </c>
       <c r="C2600" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2600" t="n">
         <v>1.38999998569489</v>
       </c>
-      <c r="D2600" t="n">
-        <v>1.3400000333786</v>
-      </c>
       <c r="E2600" t="n">
-        <v>1.37999999523163</v>
-      </c>
-      <c r="F2600" t="n">
         <v>1.38999998569489</v>
       </c>
+      <c r="F2600"/>
       <c r="G2600" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="H2600" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" s="1" t="n">
+        <v>46106.3905787037</v>
+      </c>
+      <c r="B2601" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2601" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="D2601" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="E2601" t="n">
+        <v>1.38999998569489</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>1.4099999666214</v>
+      </c>
+      <c r="G2601" t="s">
+        <v>440</v>
+      </c>
+      <c r="H2601" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820501327515</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138902664185</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669463157654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110829353333</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
@@ -284,40 +284,40 @@
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
     <t xml:space="preserve">2.25125002861023</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115553855896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -410,28 +410,28 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194727897644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964548110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480958938599</t>
@@ -440,52 +440,52 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649970054626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25037145614624</t>
+    <t xml:space="preserve">4.2503719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15473794937134</t>
+    <t xml:space="preserve">4.1547384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246206283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350112915039</t>
+    <t xml:space="preserve">4.30350065231323</t>
   </si>
   <si>
     <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881404876709</t>
+    <t xml:space="preserve">4.30881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661594390869</t>
+    <t xml:space="preserve">4.18661642074585</t>
   </si>
   <si>
     <t xml:space="preserve">4.33892107009888</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,52 +683,52 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69366,9 +69366,11 @@
       <c r="E2600" t="n">
         <v>1.38999998569489</v>
       </c>
-      <c r="F2600"/>
+      <c r="F2600" t="n">
+        <v>1.4099999666214</v>
+      </c>
       <c r="G2600" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="H2600" t="s">
         <v>9</v>
@@ -69376,27 +69378,51 @@
     </row>
     <row r="2601">
       <c r="A2601" s="1" t="n">
-        <v>46106.3905787037</v>
+        <v>46107.3333333333</v>
       </c>
       <c r="B2601" t="n">
-        <v>600</v>
+        <v>2100</v>
       </c>
       <c r="C2601" t="n">
-        <v>1.4099999666214</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="D2601" t="n">
-        <v>1.38999998569489</v>
+        <v>1.37999999523163</v>
       </c>
       <c r="E2601" t="n">
-        <v>1.38999998569489</v>
-      </c>
-      <c r="F2601" t="n">
-        <v>1.4099999666214</v>
-      </c>
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2601"/>
       <c r="G2601" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="H2601" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" s="1" t="n">
+        <v>46107.3451041667</v>
+      </c>
+      <c r="B2602" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C2602" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D2602" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E2602" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="G2602" t="s">
+        <v>467</v>
+      </c>
+      <c r="H2602" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -95,58 +95,58 @@
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
@@ -158,55 +158,55 @@
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237819671631</t>
+    <t xml:space="preserve">2.03237843513489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444614887238</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941842079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087432861328</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462953567505</t>
+    <t xml:space="preserve">2.33462929725647</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096013069153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -443,43 +443,43 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649946212769</t>
+    <t xml:space="preserve">3.32649922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69531,7 +69531,7 @@
     </row>
     <row r="2607">
       <c r="A2607" s="1" t="n">
-        <v>46119.6387384259</v>
+        <v>46119.2916666667</v>
       </c>
       <c r="B2607" t="n">
         <v>1200</v>
@@ -69552,6 +69552,32 @@
         <v>466</v>
       </c>
       <c r="H2607" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" s="1" t="n">
+        <v>46120.2916666667</v>
+      </c>
+      <c r="B2608" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2608" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2608" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E2608" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2608" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G2608" t="s">
+        <v>466</v>
+      </c>
+      <c r="H2608" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.16472816467285</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791776657104</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
     <t xml:space="preserve">1.91078317165375</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941842079163</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162525177002</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.32420682907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096013069153</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69581,6 +69581,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2609">
+      <c r="A2609" s="1" t="n">
+        <v>46121.2916666667</v>
+      </c>
+      <c r="B2609" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2609" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2609" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E2609" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2609" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2609" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211264610291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368955612183</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2287437915802</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157410621643</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401329994202</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634378433228</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561299324036</t>
+    <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692764282227</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998571872711</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693347454071</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613042831421</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242294311523</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636689186096</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542675018311</t>
+    <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
     <t xml:space="preserve">2.3242073059082</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044317245483</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194727897644</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339747428894</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335070610046</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296745300293</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693605422974</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
     <t xml:space="preserve">4.03785228729248</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754703521729</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69633,6 +69633,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2611">
+      <c r="A2611" s="1" t="n">
+        <v>46125.2916666667</v>
+      </c>
+      <c r="B2611" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2611" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D2611" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E2611" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F2611" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G2611" t="s">
+        <v>465</v>
+      </c>
+      <c r="H2611" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422857284546</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,46 +62,46 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429738044739</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,22 +146,22 @@
     <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.31031036376953</t>
@@ -176,49 +176,49 @@
     <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
     <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303093910217</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669415473938</t>
@@ -278,37 +278,37 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,49 +317,49 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124955177307</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.32420682907104</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.68378162384033</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -377,28 +377,28 @@
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124086380005</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016291618347</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387040138245</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,22 +461,22 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
     <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
     <t xml:space="preserve">3.90668296813965</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69737,6 +69737,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2615">
+      <c r="A2615" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B2615" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2615" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D2615" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E2615" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2615" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G2615" t="s">
+        <v>433</v>
+      </c>
+      <c r="H2615" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,55 +62,55 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418962478638</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576725006104</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,46 +173,46 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420980453491</t>
+    <t xml:space="preserve">1.95421016216278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -263,25 +263,25 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425455093384</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420682907104</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987599372864</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -69763,6 +69763,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2616">
+      <c r="A2616" s="1" t="n">
+        <v>46132.2916666667</v>
+      </c>
+      <c r="B2616" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C2616" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2616" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E2616" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F2616" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G2616" t="s">
+        <v>431</v>
+      </c>
+      <c r="H2616" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.22874331474304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.18157434463501</t>
@@ -77,64 +77,64 @@
     <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418962478638</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576725006104</t>
+    <t xml:space="preserve">2.10576677322388</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085947990417</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421016216278</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519647598267</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,46 +263,46 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -365,46 +365,46 @@
     <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987599372864</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32121086120605</t>
+    <t xml:space="preserve">4.3212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547033309937</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.16182136535645</t>
@@ -608,25 +608,25 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.42747020721436</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.8430438041687</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456895828247</t>
+    <t xml:space="preserve">4.60456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39205026626587</t>
+    <t xml:space="preserve">4.39204978942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69789,6 +69789,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2617">
+      <c r="A2617" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B2617" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C2617" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D2617" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E2617" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F2617" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>429</v>
+      </c>
+      <c r="H2617" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
     <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874331474304</t>
+    <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688208580017</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085947990417</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -155,43 +155,43 @@
     <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
@@ -200,25 +200,25 @@
     <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693359375</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594418525696</t>
+    <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -338,88 +338,88 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.692467212677</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091586112976</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546578407288</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.37861180305481</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387040138245</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -464,28 +464,28 @@
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3212103843689</t>
+    <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.42392778396606</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
     <t xml:space="preserve">4.33006525039673</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609664916992</t>
+    <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953205108643</t>
+    <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431081771851</t>
+    <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">3.95107388496399</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8430438041687</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60456848144531</t>
+    <t xml:space="preserve">4.60456895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39204978942871</t>
+    <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69815,6 +69815,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2618">
+      <c r="A2618" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B2618" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C2618" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2618" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2618" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="F2618" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2618" t="s">
+        <v>458</v>
+      </c>
+      <c r="H2618" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684337615967</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
     <t xml:space="preserve">2.10576701164246</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268941879272</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429858207703</t>
+    <t xml:space="preserve">2.61429834365845</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138902664185</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434606552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
     <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026335716248</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166952133179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537724494934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020694732666</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
     <t xml:space="preserve">3.17016267776489</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,34 +446,34 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762513160706</t>
+    <t xml:space="preserve">3.47762537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
     <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945889472961</t>
+    <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634378433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738215446472</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745167732239</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693359375</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.76139450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -242,31 +242,31 @@
     <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434606552124</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706961631775</t>
@@ -281,58 +281,58 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373759269714</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32594394683838</t>
+    <t xml:space="preserve">2.32594418525696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.692467212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61603569984436</t>
@@ -362,43 +362,43 @@
     <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166952133179</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706711769104</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546578407288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415089607239</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47762537002563</t>
+    <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706068992615</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7017080783844</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25037145614624</t>
+    <t xml:space="preserve">4.2503719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15473794937134</t>
+    <t xml:space="preserve">4.1547384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246206283569</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30350112915039</t>
+    <t xml:space="preserve">4.30350065231323</t>
   </si>
   <si>
     <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30881404876709</t>
+    <t xml:space="preserve">4.30881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">4.25214242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20609617233276</t>
+    <t xml:space="preserve">4.20609664916992</t>
   </si>
   <si>
     <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18661594390869</t>
+    <t xml:space="preserve">4.18661642074585</t>
   </si>
   <si>
     <t xml:space="preserve">4.33892107009888</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -683,52 +683,52 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17953157424927</t>
+    <t xml:space="preserve">4.17953205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03431129455566</t>
+    <t xml:space="preserve">4.03431081771851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -69841,6 +69841,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2619">
+      <c r="A2619" s="1" t="n">
+        <v>46135.2916666667</v>
+      </c>
+      <c r="B2619" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2619" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D2619" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2619" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F2619" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2619" t="s">
+        <v>458</v>
+      </c>
+      <c r="H2619" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" s="1" t="n">
+        <v>46136.2916666667</v>
+      </c>
+      <c r="B2620" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C2620" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="D2620" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2620" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F2620" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="G2620" t="s">
+        <v>424</v>
+      </c>
+      <c r="H2620" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684385299683</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22874355316162</t>
+    <t xml:space="preserve">2.2287437915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
@@ -80,31 +80,31 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3163435459137</t>
+    <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
     <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44269013404846</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,40 +173,40 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31899571418762</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
     <t xml:space="preserve">2.57087159156799</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -374,37 +374,37 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537724494934</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211336135864</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630507469177</t>
+    <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -98,31 +98,31 @@
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576677322388</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085947990417</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61429834365845</t>
+    <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
     <t xml:space="preserve">2.60561323165894</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
     <t xml:space="preserve">2.39716410636902</t>
@@ -170,55 +170,55 @@
     <t xml:space="preserve">2.21477150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1887149810791</t>
+    <t xml:space="preserve">2.18871521949768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03237843513489</t>
+    <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420968532562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129989147186</t>
+    <t xml:space="preserve">1.84129977226257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847899436951</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941842079163</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401784896851</t>
+    <t xml:space="preserve">2.48401761054993</t>
   </si>
   <si>
     <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373735427856</t>
+    <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636665344238</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
     <t xml:space="preserve">2.22519373893738</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382863044739</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298369407654</t>
+    <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
     <t xml:space="preserve">2.57955718040466</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537676811218</t>
+    <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
     <t xml:space="preserve">2.84706664085388</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096013069153</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2135899066925</t>
+    <t xml:space="preserve">3.21358942985535</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175806045532</t>
+    <t xml:space="preserve">3.29175782203674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
     <t xml:space="preserve">3.28480982780457</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072414398193</t>
+    <t xml:space="preserve">3.43072390556335</t>
   </si>
   <si>
     <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32649922370911</t>
+    <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.56100463867188</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162265777588</t>
+    <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400556564331</t>
+    <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930212020874</t>
+    <t xml:space="preserve">4.52930164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160779953003</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1883864402771</t>
+    <t xml:space="preserve">4.18838691711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006572723389</t>
+    <t xml:space="preserve">4.33006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515069961548</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.16713428497314</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97586822509766</t>
+    <t xml:space="preserve">3.9758677482605</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576144218445</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472309112549</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411211013794</t>
+    <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107412338257</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930362701416</t>
+    <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388344764709</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304404258728</t>
+    <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434005737305</t>
+    <t xml:space="preserve">4.37434053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014255523682</t>
+    <t xml:space="preserve">4.02014303207397</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134683609009</t>
+    <t xml:space="preserve">4.24134731292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15110540390015</t>
+    <t xml:space="preserve">4.1511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207160949707</t>
+    <t xml:space="preserve">4.51207113265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378141403198</t>
+    <t xml:space="preserve">4.40378189086914</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086444854736</t>
+    <t xml:space="preserve">4.06086397171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818819999695</t>
+    <t xml:space="preserve">3.80818796157837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013991355896</t>
+    <t xml:space="preserve">3.79013967514038</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893299102783</t>
+    <t xml:space="preserve">3.33893275260925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527075767517</t>
+    <t xml:space="preserve">3.46527099609375</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575362205505</t>
+    <t xml:space="preserve">3.64575386047363</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601554870605</t>
+    <t xml:space="preserve">2.99601531028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651843070984</t>
+    <t xml:space="preserve">2.43651866912842</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114639282227</t>
+    <t xml:space="preserve">2.67114615440369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504981994629</t>
+    <t xml:space="preserve">2.63504958152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261500358582</t>
+    <t xml:space="preserve">2.47261524200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3462769985199</t>
+    <t xml:space="preserve">2.34627723693848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408385276794</t>
+    <t xml:space="preserve">2.27408409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603580474854</t>
+    <t xml:space="preserve">2.25603556632996</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555270195007</t>
+    <t xml:space="preserve">2.07555294036865</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726334095001</t>
+    <t xml:space="preserve">1.96726310253143</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287681102753</t>
+    <t xml:space="preserve">1.82287693023682</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360122680664</t>
+    <t xml:space="preserve">2.09360098838806</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969779968262</t>
+    <t xml:space="preserve">2.12969756126404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993923187256</t>
+    <t xml:space="preserve">2.21993899345398</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189070701599</t>
+    <t xml:space="preserve">2.20189094543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213237762451</t>
+    <t xml:space="preserve">2.29213213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432552337646</t>
+    <t xml:space="preserve">2.36432528495789</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31018042564392</t>
+    <t xml:space="preserve">2.3101806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822895050049</t>
+    <t xml:space="preserve">2.32822871208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406359672546</t>
+    <t xml:space="preserve">3.01406383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454669952393</t>
+    <t xml:space="preserve">3.19454646110535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15845012664795</t>
+    <t xml:space="preserve">3.15844988822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649817466736</t>
+    <t xml:space="preserve">3.17649841308594</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796702384949</t>
+    <t xml:space="preserve">2.97796726226807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9238224029541</t>
+    <t xml:space="preserve">2.92382216453552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187045097351</t>
+    <t xml:space="preserve">2.94187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95991897583008</t>
+    <t xml:space="preserve">2.9599187374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79748439788818</t>
+    <t xml:space="preserve">2.7974841594696</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798727989197</t>
+    <t xml:space="preserve">2.23798751831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188057899475</t>
+    <t xml:space="preserve">2.57188081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163938522339</t>
+    <t xml:space="preserve">2.48163914680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554281234741</t>
+    <t xml:space="preserve">2.44554257392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211336135864</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684361457825</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.0552282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401329994202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268989562988</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -149,67 +149,67 @@
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796155929565</t>
+    <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477150917053</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18871521949768</t>
+    <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95420968532562</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84129977226257</t>
+    <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998559951782</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
     <t xml:space="preserve">1.85693371295929</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -245,52 +245,52 @@
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800904273987</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48401761054993</t>
+    <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988813400269</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33462929725647</t>
+    <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153100013733</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087135314941</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
@@ -383,70 +383,70 @@
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358942985535</t>
+    <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29175782203674</t>
+    <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43072390556335</t>
+    <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,40 +455,40 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987670898438</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668272972107</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -69997,6 +69997,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2625">
+      <c r="A2625" s="1" t="n">
+        <v>46146.2916666667</v>
+      </c>
+      <c r="B2625" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2625" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D2625" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="E2625" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F2625" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2625" t="s">
+        <v>426</v>
+      </c>
+      <c r="H2625" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" s="1" t="n">
+        <v>46147.2916666667</v>
+      </c>
+      <c r="B2626" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C2626" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D2626" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E2626" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F2626" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="G2626" t="s">
+        <v>429</v>
+      </c>
+      <c r="H2626" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211264610291</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">2.13945913314819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
     <t xml:space="preserve">2.05522847175598</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.31634330749512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738215446472</t>
+    <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788246154785</t>
+    <t xml:space="preserve">2.14788222312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472816467285</t>
+    <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
     <t xml:space="preserve">2.17820525169373</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44269013404846</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
     <t xml:space="preserve">2.5621862411499</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505176544189</t>
+    <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95421004295349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519659519196</t>
+    <t xml:space="preserve">1.85519647598267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050231933594</t>
+    <t xml:space="preserve">1.78050220012665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444614887238</t>
+    <t xml:space="preserve">1.75444626808167</t>
   </si>
   <si>
     <t xml:space="preserve">1.76139461994171</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138878822327</t>
+    <t xml:space="preserve">2.50138854980469</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
@@ -245,46 +245,46 @@
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800928115845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613042831421</t>
+    <t xml:space="preserve">2.53613018989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669439315796</t>
+    <t xml:space="preserve">2.42669415473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331512451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768130302429</t>
+    <t xml:space="preserve">2.32768106460571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674163818359</t>
+    <t xml:space="preserve">2.38674139976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636689186096</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3502631187439</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4145348072052</t>
+    <t xml:space="preserve">2.41453504562378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153052330017</t>
+    <t xml:space="preserve">2.38153076171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3242073059082</t>
+    <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382886886597</t>
+    <t xml:space="preserve">2.64382863044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.69246697425842</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772557258606</t>
+    <t xml:space="preserve">2.65772533416748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77063536643982</t>
+    <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74110507965088</t>
+    <t xml:space="preserve">2.7411048412323</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537700653076</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889229774475</t>
+    <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020718574524</t>
+    <t xml:space="preserve">3.50020742416382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124110221863</t>
+    <t xml:space="preserve">3.36124086380005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,55 +413,55 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701642036438</t>
+    <t xml:space="preserve">3.25701665878296</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861204147339</t>
+    <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218052864075</t>
+    <t xml:space="preserve">3.30218076705933</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100463867188</t>
+    <t xml:space="preserve">3.5610044002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.4758882522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508734703064</t>
+    <t xml:space="preserve">3.78508710861206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -70101,6 +70101,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2629">
+      <c r="A2629" s="1" t="n">
+        <v>46150.2916666667</v>
+      </c>
+      <c r="B2629" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2629" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D2629" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2629" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F2629" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2629" t="s">
+        <v>458</v>
+      </c>
+      <c r="H2629" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895906448364</t>
+    <t xml:space="preserve">2.24895930290222</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211288452148</t>
+    <t xml:space="preserve">2.23211312294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684385299683</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">2.15630531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13945913314819</t>
+    <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522847175598</t>
+    <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
     <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688184738159</t>
+    <t xml:space="preserve">2.36688208580017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31634330749512</t>
+    <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
     <t xml:space="preserve">2.25738191604614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
     <t xml:space="preserve">2.11418986320496</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831300735474</t>
+    <t xml:space="preserve">2.18831324577332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44269013404846</t>
+    <t xml:space="preserve">2.44268941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007413864136</t>
+    <t xml:space="preserve">2.51007437705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692811965942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664714813232</t>
+    <t xml:space="preserve">2.4666473865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">2.34505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21477127075195</t>
@@ -173,49 +173,49 @@
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1713445186615</t>
+    <t xml:space="preserve">2.17134428024292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791776657104</t>
+    <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0410635471344</t>
+    <t xml:space="preserve">2.04106378555298</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078317165375</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
     <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95421004295349</t>
+    <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683922290802</t>
+    <t xml:space="preserve">1.93683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85519647598267</t>
+    <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050220012665</t>
+    <t xml:space="preserve">1.78050243854523</t>
   </si>
   <si>
     <t xml:space="preserve">1.75444626808167</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138854980469</t>
+    <t xml:space="preserve">2.50138902664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847851753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800928115845</t>
+    <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613018989563</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706937789917</t>
+    <t xml:space="preserve">2.47706961631775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42669415473938</t>
+    <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.37110805511475</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331512451172</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087456703186</t>
+    <t xml:space="preserve">2.20087432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768106460571</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.3363664150238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3502631187439</t>
+    <t xml:space="preserve">2.35026335716248</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">2.39542698860168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30857348442078</t>
+    <t xml:space="preserve">2.3085732460022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41453504562378</t>
+    <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.38153076171875</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33115530014038</t>
+    <t xml:space="preserve">2.3311550617218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64382863044739</t>
+    <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246697425842</t>
+    <t xml:space="preserve">2.69246673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65772533416748</t>
+    <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7706356048584</t>
@@ -386,37 +386,37 @@
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889253616333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020742416382</t>
+    <t xml:space="preserve">3.50020694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36124086380005</t>
+    <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185255050659</t>
+    <t xml:space="preserve">3.21185278892517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701665878296</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415113449097</t>
+    <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218076705933</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5610044002533</t>
+    <t xml:space="preserve">3.56100487709045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4758882522583</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -464,28 +464,28 @@
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.70170760154724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339747428894</t>
+    <t xml:space="preserve">3.7433979511261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987623214722</t>
+    <t xml:space="preserve">3.7798764705658</t>
   </si>
   <si>
     <t xml:space="preserve">3.78334999084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78508710861206</t>
+    <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668249130249</t>
+    <t xml:space="preserve">3.90668296813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0821270942688</t>
+    <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
     <t xml:space="preserve">4.07327222824097</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296745300293</t>
+    <t xml:space="preserve">4.15296697616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579092025757</t>
+    <t xml:space="preserve">4.28579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769863128662</t>
+    <t xml:space="preserve">4.65769910812378</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266172409058</t>
+    <t xml:space="preserve">4.23266124725342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160875320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693605422974</t>
+    <t xml:space="preserve">4.27693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10514974594116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243282318115</t>
+    <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.1671347618103</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0555624961853</t>
+    <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785228729248</t>
+    <t xml:space="preserve">4.03785276412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472285270691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754703521729</t>
+    <t xml:space="preserve">4.11754751205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42747020721436</t>
+    <t xml:space="preserve">4.4274697303772</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786762237549</t>
+    <t xml:space="preserve">4.20786714553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495151519775</t>
+    <t xml:space="preserve">4.21495199203491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858562469482</t>
+    <t xml:space="preserve">4.07858514785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525724411011</t>
+    <t xml:space="preserve">4.13525772094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107388496399</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533407211304</t>
   </si>
   <si>
     <t xml:space="preserve">3.96701312065125</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869216918945</t>
+    <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
     <t xml:space="preserve">4.40975999832153</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -70127,6 +70127,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2630">
+      <c r="A2630" s="1" t="n">
+        <v>46153.2916666667</v>
+      </c>
+      <c r="B2630" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C2630" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D2630" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E2630" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2630" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2630" t="s">
+        <v>458</v>
+      </c>
+      <c r="H2630" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422833442688</t>
+    <t xml:space="preserve">2.27422857284546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23211312294006</t>
+    <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22369003295898</t>
+    <t xml:space="preserve">2.22368979454041</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630531311035</t>
+    <t xml:space="preserve">2.15630555152893</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157434463501</t>
+    <t xml:space="preserve">2.18157458305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.12261319160461</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">2.05522871017456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401306152344</t>
+    <t xml:space="preserve">2.25401282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36688208580017</t>
+    <t xml:space="preserve">2.36688184738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.3163435459137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25738191604614</t>
+    <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
     <t xml:space="preserve">2.24053597450256</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18831324577332</t>
+    <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
     <t xml:space="preserve">2.10745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10576701164246</t>
+    <t xml:space="preserve">2.1057665348053</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820501327515</t>
+    <t xml:space="preserve">2.1782054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27085900306702</t>
+    <t xml:space="preserve">2.2708592414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44268941879272</t>
+    <t xml:space="preserve">2.4426896572113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51007437705994</t>
+    <t xml:space="preserve">2.51007413864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.61429858207703</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692811965942</t>
+    <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875948905945</t>
+    <t xml:space="preserve">2.51875972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56218647956848</t>
+    <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4666473865509</t>
+    <t xml:space="preserve">2.46664690971375</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39716410636902</t>
+    <t xml:space="preserve">2.3971643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34505200386047</t>
+    <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031060218811</t>
+    <t xml:space="preserve">2.31031036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477127075195</t>
+    <t xml:space="preserve">2.21477103233337</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265892982483</t>
+    <t xml:space="preserve">2.16265916824341</t>
   </si>
   <si>
     <t xml:space="preserve">2.10186147689819</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078305244446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542099237442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683934211731</t>
+    <t xml:space="preserve">1.93683910369873</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -212,58 +212,58 @@
     <t xml:space="preserve">1.84998548030853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693383216858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78050243854523</t>
+    <t xml:space="preserve">1.78050231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75444626808167</t>
+    <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76139461994171</t>
+    <t xml:space="preserve">1.761394739151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824526786804</t>
+    <t xml:space="preserve">2.21824550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31899571418762</t>
+    <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50138902664185</t>
+    <t xml:space="preserve">2.50138878822327</t>
   </si>
   <si>
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847851753235</t>
+    <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941818237305</t>
+    <t xml:space="preserve">2.32941794395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64903998374939</t>
+    <t xml:space="preserve">2.64904022216797</t>
   </si>
   <si>
     <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303141593933</t>
+    <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650517463684</t>
+    <t xml:space="preserve">2.58650541305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53613018989563</t>
+    <t xml:space="preserve">2.53612995147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110805511475</t>
+    <t xml:space="preserve">2.37110781669617</t>
   </si>
   <si>
     <t xml:space="preserve">2.28425431251526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162501335144</t>
+    <t xml:space="preserve">2.30162525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242270469666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20087432861328</t>
+    <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
     <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32768106460571</t>
+    <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
     <t xml:space="preserve">2.38674139976501</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3363664150238</t>
+    <t xml:space="preserve">2.33636665344238</t>
   </si>
   <si>
     <t xml:space="preserve">2.35026335716248</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25125002861023</t>
+    <t xml:space="preserve">2.25124979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519373893738</t>
+    <t xml:space="preserve">2.22519397735596</t>
   </si>
   <si>
     <t xml:space="preserve">2.32420706748962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3311550617218</t>
+    <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64035487174988</t>
+    <t xml:space="preserve">2.6403546333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955694198608</t>
+    <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378162384033</t>
+    <t xml:space="preserve">2.68378186225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166928291321</t>
+    <t xml:space="preserve">2.63166904449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">2.7706356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7411048412323</t>
+    <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706687927246</t>
   </si>
   <si>
     <t xml:space="preserve">2.90091609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110210418701</t>
+    <t xml:space="preserve">3.11110234260559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044364929199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50889253616333</t>
+    <t xml:space="preserve">3.50889229774475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50020694732666</t>
+    <t xml:space="preserve">3.50020718574524</t>
   </si>
   <si>
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21185278892517</t>
+    <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.13194704055786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25701665878296</t>
+    <t xml:space="preserve">3.25701642036438</t>
   </si>
   <si>
     <t xml:space="preserve">3.17884826660156</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.37861180305481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.34387016296387</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218076705933</t>
+    <t xml:space="preserve">3.30218029022217</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56100487709045</t>
+    <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588777542114</t>
+    <t xml:space="preserve">3.47588801383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">3.58706092834473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170760154724</t>
+    <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7433979511261</t>
+    <t xml:space="preserve">3.74339771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7798764705658</t>
+    <t xml:space="preserve">3.77987694740295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78334999084473</t>
+    <t xml:space="preserve">3.78335022926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">4.08212757110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913415908813</t>
+    <t xml:space="preserve">4.39913463592529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65769910812378</t>
+    <t xml:space="preserve">4.65769863128662</t>
   </si>
   <si>
     <t xml:space="preserve">4.58243179321289</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246253967285</t>
+    <t xml:space="preserve">4.34246301651001</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2946457862854</t>
+    <t xml:space="preserve">4.29464626312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.30350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23266124725342</t>
+    <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160875320435</t>
+    <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693557739258</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892107009888</t>
+    <t xml:space="preserve">4.33892059326172</t>
   </si>
   <si>
     <t xml:space="preserve">4.23797416687012</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10514974594116</t>
+    <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243330001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067718505859</t>
+    <t xml:space="preserve">4.17067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.04316568374634</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472285270691</t>
+    <t xml:space="preserve">3.98472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754751205444</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3725700378418</t>
+    <t xml:space="preserve">4.37256956100464</t>
   </si>
   <si>
     <t xml:space="preserve">4.4274697303772</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.16005086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20786714553833</t>
+    <t xml:space="preserve">4.20786762237549</t>
   </si>
   <si>
     <t xml:space="preserve">4.23443269729614</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663080215454</t>
+    <t xml:space="preserve">4.35663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21495199203491</t>
+    <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.07858514785767</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">4.17953157424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13525772094727</t>
+    <t xml:space="preserve">4.13525724411011</t>
   </si>
   <si>
     <t xml:space="preserve">4.03431129455566</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533407211304</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388392448425</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">4.10869169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40975999832153</t>
+    <t xml:space="preserve">4.40976047515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26808166503906</t>
+    <t xml:space="preserve">4.2680811882019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846374511719</t>
+    <t xml:space="preserve">3.87846398353577</t>
   </si>
   <si>
     <t xml:space="preserve">4.09098243713379</t>
@@ -70153,6 +70153,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2631">
+      <c r="A2631" s="1" t="n">
+        <v>46154.2916666667</v>
+      </c>
+      <c r="B2631" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C2631" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D2631" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2631" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F2631" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G2631" t="s">
+        <v>431</v>
+      </c>
+      <c r="H2631" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27422857284546</t>
+    <t xml:space="preserve">2.2742280960083</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684337615967</t>
+    <t xml:space="preserve">2.20684361457825</t>
   </si>
   <si>
     <t xml:space="preserve">2.22368979454041</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">2.22874355316162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15630555152893</t>
+    <t xml:space="preserve">2.15630507469177</t>
   </si>
   <si>
     <t xml:space="preserve">2.13945889472961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18157458305359</t>
+    <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261319160461</t>
+    <t xml:space="preserve">2.12261295318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09734392166138</t>
+    <t xml:space="preserve">2.0973436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05522871017456</t>
+    <t xml:space="preserve">2.0552282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401282310486</t>
+    <t xml:space="preserve">2.25401329994202</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053597450256</t>
+    <t xml:space="preserve">2.24053621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315125465393</t>
+    <t xml:space="preserve">2.17315149307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429761886597</t>
+    <t xml:space="preserve">2.12429785728455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11419010162354</t>
+    <t xml:space="preserve">2.11418986320496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103604316711</t>
+    <t xml:space="preserve">2.13103628158569</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10745143890381</t>
+    <t xml:space="preserve">2.10745167732239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1057665348053</t>
+    <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
     <t xml:space="preserve">2.14788222312927</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">2.16472840309143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1782054901123</t>
+    <t xml:space="preserve">2.17820525169373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2708592414856</t>
+    <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845899581909</t>
+    <t xml:space="preserve">2.35845875740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.4426896572113</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">2.60561323165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60387587547302</t>
+    <t xml:space="preserve">2.6038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">2.59692788124084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51875972747803</t>
+    <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
     <t xml:space="preserve">2.5621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46664690971375</t>
+    <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.45796179771423</t>
@@ -164,37 +164,37 @@
     <t xml:space="preserve">2.34505176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31031036376953</t>
+    <t xml:space="preserve">2.31031060218811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21477103233337</t>
+    <t xml:space="preserve">2.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17134428024292</t>
+    <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12791752815247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16265916824341</t>
+    <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186147689819</t>
+    <t xml:space="preserve">2.10186123847961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04106378555298</t>
+    <t xml:space="preserve">2.0410635471344</t>
   </si>
   <si>
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078305244446</t>
+    <t xml:space="preserve">1.91078329086304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.867356300354</t>
+    <t xml:space="preserve">1.86735618114471</t>
   </si>
   <si>
     <t xml:space="preserve">1.9542099237442</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998548030853</t>
+    <t xml:space="preserve">1.84998536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693383216858</t>
+    <t xml:space="preserve">1.85693371295929</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">1.75444614887238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.761394739151</t>
+    <t xml:space="preserve">1.76139461994171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21824550628662</t>
+    <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.3189959526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584945678711</t>
+    <t xml:space="preserve">2.40584969520569</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -242,28 +242,28 @@
     <t xml:space="preserve">2.38847875595093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32941794395447</t>
+    <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190574645996</t>
+    <t xml:space="preserve">2.43190550804138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64904022216797</t>
+    <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434582710266</t>
+    <t xml:space="preserve">2.57434558868408</t>
   </si>
   <si>
     <t xml:space="preserve">2.58303117752075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650541305542</t>
+    <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.41800880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53612995147705</t>
+    <t xml:space="preserve">2.53613042831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.48401784896851</t>
@@ -275,40 +275,40 @@
     <t xml:space="preserve">2.42669439315796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37110781669617</t>
+    <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425431251526</t>
+    <t xml:space="preserve">2.28425407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30162525177002</t>
+    <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331488609314</t>
+    <t xml:space="preserve">2.34331464767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242270469666</t>
+    <t xml:space="preserve">2.36242246627808</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988789558411</t>
+    <t xml:space="preserve">2.29988813400269</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38674139976501</t>
+    <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
     <t xml:space="preserve">2.35373711585999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33636665344238</t>
+    <t xml:space="preserve">2.33636689186096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35026335716248</t>
+    <t xml:space="preserve">2.3502631187439</t>
   </si>
   <si>
     <t xml:space="preserve">2.33462953567505</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">2.4145348072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38153076171875</t>
+    <t xml:space="preserve">2.38153052330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.32594394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25124979019165</t>
+    <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22519397735596</t>
+    <t xml:space="preserve">2.2251935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32420706748962</t>
+    <t xml:space="preserve">2.3242073059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.33115530014038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6403546333313</t>
+    <t xml:space="preserve">2.64035487174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.64382886886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69246673583984</t>
+    <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603569984436</t>
+    <t xml:space="preserve">2.61603593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087159156799</t>
+    <t xml:space="preserve">2.57087182998657</t>
   </si>
   <si>
     <t xml:space="preserve">2.62298393249512</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.57955718040466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378186225891</t>
+    <t xml:space="preserve">2.68378138542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63166904449463</t>
+    <t xml:space="preserve">2.63166928291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.65772557258606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7706356048584</t>
+    <t xml:space="preserve">2.77063536643982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74110507965088</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">2.80537700653076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706687927246</t>
+    <t xml:space="preserve">2.84706664085388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091609954834</t>
+    <t xml:space="preserve">2.90091633796692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11110234260559</t>
+    <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044364929199</t>
+    <t xml:space="preserve">3.30044341087341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4654655456543</t>
+    <t xml:space="preserve">3.46546530723572</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096036911011</t>
+    <t xml:space="preserve">3.23096060752869</t>
   </si>
   <si>
     <t xml:space="preserve">3.21358966827393</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016291618347</t>
+    <t xml:space="preserve">3.17016267776489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194704055786</t>
+    <t xml:space="preserve">3.13194680213928</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2396457195282</t>
+    <t xml:space="preserve">3.23964595794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37861180305481</t>
+    <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480982780457</t>
+    <t xml:space="preserve">3.28480958938599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34387016296387</t>
+    <t xml:space="preserve">3.34386992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">3.47415089607239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30218029022217</t>
+    <t xml:space="preserve">3.30218052864075</t>
   </si>
   <si>
     <t xml:space="preserve">3.32649946212769</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">3.56100463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47588801383972</t>
+    <t xml:space="preserve">3.47588777542114</t>
   </si>
   <si>
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706092834473</t>
+    <t xml:space="preserve">3.58706116676331</t>
   </si>
   <si>
     <t xml:space="preserve">3.70170783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74339771270752</t>
+    <t xml:space="preserve">3.74339747428894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77987694740295</t>
+    <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335022926331</t>
+    <t xml:space="preserve">3.78335046768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.03870058059692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08212757110596</t>
+    <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327270507812</t>
+    <t xml:space="preserve">4.07327222824097</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">4.27162313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15296697616577</t>
+    <t xml:space="preserve">4.15296745300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.25037145614624</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">4.15473794937134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28579139709473</t>
+    <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
     <t xml:space="preserve">4.11400508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39913463592529</t>
+    <t xml:space="preserve">4.39913415908813</t>
   </si>
   <si>
     <t xml:space="preserve">4.65769863128662</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517993927002</t>
+    <t xml:space="preserve">4.44517946243286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34246301651001</t>
+    <t xml:space="preserve">4.34246253967285</t>
   </si>
   <si>
     <t xml:space="preserve">4.48059988021851</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.42569923400879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29464626312256</t>
+    <t xml:space="preserve">4.2946457862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392778396606</t>
+    <t xml:space="preserve">4.42392826080322</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">4.10160827636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27693557739258</t>
+    <t xml:space="preserve">4.27693605422974</t>
   </si>
   <si>
     <t xml:space="preserve">4.22380638122559</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547080993652</t>
+    <t xml:space="preserve">4.19547033309937</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33892059326172</t>
+    <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797416687012</t>
+    <t xml:space="preserve">4.23797464370728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3902792930603</t>
+    <t xml:space="preserve">4.39027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1618218421936</t>
+    <t xml:space="preserve">4.16182136535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10515022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00243330001831</t>
+    <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16713428497314</t>
+    <t xml:space="preserve">4.1671347618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983730316162</t>
+    <t xml:space="preserve">4.09983777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05556201934814</t>
+    <t xml:space="preserve">4.0555624961853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17067670822144</t>
+    <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316568374634</t>
+    <t xml:space="preserve">4.04316520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03785276412964</t>
+    <t xml:space="preserve">4.03785228729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.96524238586426</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576096534729</t>
+    <t xml:space="preserve">3.94576120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472261428833</t>
+    <t xml:space="preserve">3.98472332954407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11754751205444</t>
+    <t xml:space="preserve">4.11754703521729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899789810181</t>
+    <t xml:space="preserve">4.02899837493896</t>
   </si>
   <si>
     <t xml:space="preserve">4.14411163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724130630493</t>
+    <t xml:space="preserve">4.19724178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37256956100464</t>
+    <t xml:space="preserve">4.3725700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4274697303772</t>
+    <t xml:space="preserve">4.42747020721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16005086898804</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942455291748</t>
+    <t xml:space="preserve">4.14942502975464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35663032531738</t>
+    <t xml:space="preserve">4.35663080215454</t>
   </si>
   <si>
     <t xml:space="preserve">4.15827989578247</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.21495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07858514785767</t>
+    <t xml:space="preserve">4.07858562469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.17953157424927</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107388496399</t>
+    <t xml:space="preserve">3.95107436180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82533431053162</t>
+    <t xml:space="preserve">3.8253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701335906982</t>
+    <t xml:space="preserve">3.96701312065125</t>
   </si>
   <si>
     <t xml:space="preserve">3.94930338859558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388392448425</t>
+    <t xml:space="preserve">3.91388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">3.84304428100586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10869169235229</t>
+    <t xml:space="preserve">4.10869216918945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40976047515869</t>
+    <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.37434053421021</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601982116699</t>
+    <t xml:space="preserve">4.51601934432983</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.39205026626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680811882019</t>
+    <t xml:space="preserve">4.26808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846398353577</t>
+    <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098243713379</t>
+    <t xml:space="preserve">4.09098196029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
@@ -70164,7 +70164,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="D2631" t="n">
-        <v>1.63999998569489</v>
+        <v>1.60000002384186</v>
       </c>
       <c r="E2631" t="n">
         <v>1.63999998569489</v>
@@ -70176,6 +70176,32 @@
         <v>431</v>
       </c>
       <c r="H2631" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" s="1" t="n">
+        <v>46155.2916666667</v>
+      </c>
+      <c r="B2632" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2632" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D2632" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="E2632" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F2632" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="G2632" t="s">
+        <v>427</v>
+      </c>
+      <c r="H2632" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24895930290222</t>
+    <t xml:space="preserve">2.24895906448364</t>
   </si>
   <si>
     <t xml:space="preserve">LFG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2742280960083</t>
+    <t xml:space="preserve">2.27422833442688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20684361457825</t>
+    <t xml:space="preserve">2.20684337615967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22368979454041</t>
+    <t xml:space="preserve">2.22369003295898</t>
   </si>
   <si>
     <t xml:space="preserve">2.22874355316162</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">2.18157434463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12261295318604</t>
+    <t xml:space="preserve">2.12261319160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0973436832428</t>
+    <t xml:space="preserve">2.09734392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0552282333374</t>
+    <t xml:space="preserve">2.05522847175598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25401329994202</t>
+    <t xml:space="preserve">2.25401306152344</t>
   </si>
   <si>
     <t xml:space="preserve">2.36688184738159</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">2.25738215446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24053621292114</t>
+    <t xml:space="preserve">2.24053597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17315149307251</t>
+    <t xml:space="preserve">2.17315125465393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12429785728455</t>
+    <t xml:space="preserve">2.12429761886597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11418986320496</t>
+    <t xml:space="preserve">2.11419010162354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13103628158569</t>
+    <t xml:space="preserve">2.13103604316711</t>
   </si>
   <si>
     <t xml:space="preserve">2.18831300735474</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">2.10576701164246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14788222312927</t>
+    <t xml:space="preserve">2.14788198471069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16472840309143</t>
+    <t xml:space="preserve">2.16472816467285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17820525169373</t>
+    <t xml:space="preserve">2.17820501327515</t>
   </si>
   <si>
     <t xml:space="preserve">2.27085900306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35845875740051</t>
+    <t xml:space="preserve">2.35845899581909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4426896572113</t>
+    <t xml:space="preserve">2.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">2.51007413864136</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">2.61429858207703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60561323165894</t>
+    <t xml:space="preserve">2.60561299324036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6038761138916</t>
+    <t xml:space="preserve">2.60387587547302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59692788124084</t>
+    <t xml:space="preserve">2.59692764282227</t>
   </si>
   <si>
     <t xml:space="preserve">2.51875948905945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5621862411499</t>
+    <t xml:space="preserve">2.56218647956848</t>
   </si>
   <si>
     <t xml:space="preserve">2.46664714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45796179771423</t>
+    <t xml:space="preserve">2.45796155929565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971643447876</t>
+    <t xml:space="preserve">2.39716410636902</t>
   </si>
   <si>
     <t xml:space="preserve">2.34505176544189</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.1713445186615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12791752815247</t>
+    <t xml:space="preserve">2.12791776657104</t>
   </si>
   <si>
     <t xml:space="preserve">2.16265892982483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10186123847961</t>
+    <t xml:space="preserve">2.10186147689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.0410635471344</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.03237819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91078329086304</t>
+    <t xml:space="preserve">1.91078317165375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86735618114471</t>
+    <t xml:space="preserve">1.867356300354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9542099237442</t>
+    <t xml:space="preserve">1.95420980453491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93683910369873</t>
+    <t xml:space="preserve">1.93683922290802</t>
   </si>
   <si>
     <t xml:space="preserve">1.84129989147186</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.85519659519196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84998536109924</t>
+    <t xml:space="preserve">1.84998571872711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85693371295929</t>
+    <t xml:space="preserve">1.85693347454071</t>
   </si>
   <si>
     <t xml:space="preserve">1.78050231933594</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.21824526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3189959526062</t>
+    <t xml:space="preserve">2.31899571418762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40584969520569</t>
+    <t xml:space="preserve">2.40584945678711</t>
   </si>
   <si>
     <t xml:space="preserve">2.50138878822327</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">2.36415958404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847875595093</t>
+    <t xml:space="preserve">2.38847899436951</t>
   </si>
   <si>
     <t xml:space="preserve">2.32941818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43190550804138</t>
+    <t xml:space="preserve">2.43190574645996</t>
   </si>
   <si>
     <t xml:space="preserve">2.64903998374939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57434558868408</t>
+    <t xml:space="preserve">2.57434582710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58303117752075</t>
+    <t xml:space="preserve">2.58303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650517463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41800880432129</t>
+    <t xml:space="preserve">2.41800904273987</t>
   </si>
   <si>
     <t xml:space="preserve">2.53613042831421</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.48401784896851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47706961631775</t>
+    <t xml:space="preserve">2.47706937789917</t>
   </si>
   <si>
     <t xml:space="preserve">2.42669439315796</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">2.37110805511475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28425407409668</t>
+    <t xml:space="preserve">2.28425455093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.30162501335144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34331464767456</t>
+    <t xml:space="preserve">2.34331488609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36242246627808</t>
+    <t xml:space="preserve">2.36242294311523</t>
   </si>
   <si>
     <t xml:space="preserve">2.20087456703186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29988813400269</t>
+    <t xml:space="preserve">2.29988789558411</t>
   </si>
   <si>
     <t xml:space="preserve">2.32768130302429</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.38674163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35373711585999</t>
+    <t xml:space="preserve">2.35373735427856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33636689186096</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.33462953567505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39542698860168</t>
+    <t xml:space="preserve">2.39542675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3085732460022</t>
+    <t xml:space="preserve">2.30857348442078</t>
   </si>
   <si>
     <t xml:space="preserve">2.4145348072052</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.25125002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2251935005188</t>
+    <t xml:space="preserve">2.22519373893738</t>
   </si>
   <si>
     <t xml:space="preserve">2.3242073059082</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">2.69246697425842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61603593826294</t>
+    <t xml:space="preserve">2.61603569984436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57087182998657</t>
+    <t xml:space="preserve">2.57087159156799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62298393249512</t>
+    <t xml:space="preserve">2.62298369407654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57955718040466</t>
+    <t xml:space="preserve">2.57955694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68378138542175</t>
+    <t xml:space="preserve">2.68378162384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63166928291321</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">2.74110507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80537700653076</t>
+    <t xml:space="preserve">2.80537676811218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84706664085388</t>
+    <t xml:space="preserve">2.84706711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90091633796692</t>
+    <t xml:space="preserve">2.90091586112976</t>
   </si>
   <si>
     <t xml:space="preserve">3.11110210418701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30044341087341</t>
+    <t xml:space="preserve">3.30044317245483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46546530723572</t>
+    <t xml:space="preserve">3.4654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">3.50889229774475</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">3.36124110221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23096060752869</t>
+    <t xml:space="preserve">3.23096036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21358966827393</t>
+    <t xml:space="preserve">3.2135899066925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21185255050659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17016267776489</t>
+    <t xml:space="preserve">3.17016291618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13194680213928</t>
+    <t xml:space="preserve">3.13194727897644</t>
   </si>
   <si>
     <t xml:space="preserve">3.25701642036438</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.17884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23964595794678</t>
+    <t xml:space="preserve">3.2396457195282</t>
   </si>
   <si>
     <t xml:space="preserve">3.29175806045532</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.37861204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28480958938599</t>
+    <t xml:space="preserve">3.28480982780457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34386992454529</t>
+    <t xml:space="preserve">3.34387016296387</t>
   </si>
   <si>
     <t xml:space="preserve">3.43072414398193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47415089607239</t>
+    <t xml:space="preserve">3.47415113449097</t>
   </si>
   <si>
     <t xml:space="preserve">3.30218052864075</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">3.47762513160706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58706116676331</t>
+    <t xml:space="preserve">3.58706068992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70170783996582</t>
+    <t xml:space="preserve">3.7017080783844</t>
   </si>
   <si>
     <t xml:space="preserve">3.74339747428894</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">3.77987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78335046768188</t>
+    <t xml:space="preserve">3.78335070610046</t>
   </si>
   <si>
     <t xml:space="preserve">3.78508734703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90668296813965</t>
+    <t xml:space="preserve">3.90668272972107</t>
   </si>
   <si>
     <t xml:space="preserve">4.03870058059692</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">4.0821270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07327222824097</t>
+    <t xml:space="preserve">4.07327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27162313461304</t>
+    <t xml:space="preserve">4.27162265777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.15296745300293</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">4.28579092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11400508880615</t>
+    <t xml:space="preserve">4.11400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.39913415908813</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">4.58243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52930164337158</t>
+    <t xml:space="preserve">4.52930212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.47174501419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44517946243286</t>
+    <t xml:space="preserve">4.44517993927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.34246253967285</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.32121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42392826080322</t>
+    <t xml:space="preserve">4.42392778396606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30350112915039</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">4.23266172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10160827636719</t>
+    <t xml:space="preserve">4.10160779953003</t>
   </si>
   <si>
     <t xml:space="preserve">4.27693605422974</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">4.22380638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18838691711426</t>
+    <t xml:space="preserve">4.1883864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33006525039673</t>
+    <t xml:space="preserve">4.33006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.30881404876709</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">4.20609617233276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19547033309937</t>
+    <t xml:space="preserve">4.19547080993652</t>
   </si>
   <si>
     <t xml:space="preserve">4.18661594390869</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">4.33892107009888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23797464370728</t>
+    <t xml:space="preserve">4.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39027976989746</t>
+    <t xml:space="preserve">4.3902792930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16182136535645</t>
+    <t xml:space="preserve">4.1618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10515022277832</t>
+    <t xml:space="preserve">4.10515069961548</t>
   </si>
   <si>
     <t xml:space="preserve">4.00243282318115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1671347618103</t>
+    <t xml:space="preserve">4.16713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.03076887130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09983777999878</t>
+    <t xml:space="preserve">4.09983730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.0555624961853</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.17067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04316520690918</t>
+    <t xml:space="preserve">4.04316568374634</t>
   </si>
   <si>
     <t xml:space="preserve">4.03785228729248</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.96524238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9758677482605</t>
+    <t xml:space="preserve">3.97586822509766</t>
   </si>
   <si>
     <t xml:space="preserve">3.95992946624756</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">3.95815801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94576120376587</t>
+    <t xml:space="preserve">3.94576144218445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98472332954407</t>
+    <t xml:space="preserve">3.98472309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.11754703521729</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">4.06441783905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02899837493896</t>
+    <t xml:space="preserve">4.02899789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14411163330078</t>
+    <t xml:space="preserve">4.14411211013794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19724178314209</t>
+    <t xml:space="preserve">4.19724130630493</t>
   </si>
   <si>
     <t xml:space="preserve">4.3725700378418</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.12640190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14942502975464</t>
+    <t xml:space="preserve">4.14942455291748</t>
   </si>
   <si>
     <t xml:space="preserve">4.35663080215454</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">4.03431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95107436180115</t>
+    <t xml:space="preserve">3.95107412338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.92273831367493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8253345489502</t>
+    <t xml:space="preserve">3.82533431053162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96701312065125</t>
+    <t xml:space="preserve">3.96701335906982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94930338859558</t>
+    <t xml:space="preserve">3.94930362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91388368606567</t>
+    <t xml:space="preserve">3.91388344764709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84304428100586</t>
+    <t xml:space="preserve">3.84304404258728</t>
   </si>
   <si>
     <t xml:space="preserve">4.10869216918945</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">4.40975999832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37434053421021</t>
+    <t xml:space="preserve">4.37434005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02014303207397</t>
+    <t xml:space="preserve">4.02014255523682</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51601934432983</t>
+    <t xml:space="preserve">4.51601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">4.60456895828247</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">3.87846374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09098196029663</t>
+    <t xml:space="preserve">4.09098243713379</t>
   </si>
   <si>
     <t xml:space="preserve">4.3135404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24134731292725</t>
+    <t xml:space="preserve">4.24134683609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.11500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1511058807373</t>
+    <t xml:space="preserve">4.15110540390015</t>
   </si>
   <si>
     <t xml:space="preserve">4.27744340896606</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.42183017730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51207113265991</t>
+    <t xml:space="preserve">4.51207160949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.55719232559204</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.60231304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40378189086914</t>
+    <t xml:space="preserve">4.40378141403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.64743375778198</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.16915416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06086397171021</t>
+    <t xml:space="preserve">4.06086444854736</t>
   </si>
   <si>
     <t xml:space="preserve">3.97062301635742</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.88038158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80818796157837</t>
+    <t xml:space="preserve">3.80818819999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77209162712097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79013967514038</t>
+    <t xml:space="preserve">3.79013991355896</t>
   </si>
   <si>
     <t xml:space="preserve">3.60965728759766</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.41112589836121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33893275260925</t>
+    <t xml:space="preserve">3.33893299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46527099609375</t>
+    <t xml:space="preserve">3.46527075767517</t>
   </si>
   <si>
     <t xml:space="preserve">3.69989848136902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64575386047363</t>
+    <t xml:space="preserve">3.64575362205505</t>
   </si>
   <si>
     <t xml:space="preserve">3.51941585540771</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24869132041931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99601531028748</t>
+    <t xml:space="preserve">2.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">2.72529125213623</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">2.86967754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43651866912842</t>
+    <t xml:space="preserve">2.43651843070984</t>
   </si>
   <si>
     <t xml:space="preserve">2.52676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67114615440369</t>
+    <t xml:space="preserve">2.67114639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63504958152771</t>
+    <t xml:space="preserve">2.63504981994629</t>
   </si>
   <si>
     <t xml:space="preserve">2.70724272727966</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.58090472221375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47261524200439</t>
+    <t xml:space="preserve">2.47261500358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.45456695556641</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">2.38237380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34627723693848</t>
+    <t xml:space="preserve">2.3462769985199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27408409118652</t>
+    <t xml:space="preserve">2.27408385276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25603556632996</t>
+    <t xml:space="preserve">2.25603580474854</t>
   </si>
   <si>
     <t xml:space="preserve">2.16579437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07555294036865</t>
+    <t xml:space="preserve">2.07555270195007</t>
   </si>
   <si>
     <t xml:space="preserve">1.94921493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96726310253143</t>
+    <t xml:space="preserve">1.96726334095001</t>
   </si>
   <si>
     <t xml:space="preserve">1.98531150817871</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">1.80482864379883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287693023682</t>
+    <t xml:space="preserve">1.82287681102753</t>
   </si>
   <si>
     <t xml:space="preserve">1.8589733839035</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.02140808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360098838806</t>
+    <t xml:space="preserve">2.09360122680664</t>
   </si>
   <si>
     <t xml:space="preserve">2.18384265899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12969756126404</t>
+    <t xml:space="preserve">2.12969779968262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21993899345398</t>
+    <t xml:space="preserve">2.21993923187256</t>
   </si>
   <si>
     <t xml:space="preserve">2.14774608612061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20189094543457</t>
+    <t xml:space="preserve">2.20189070701599</t>
   </si>
   <si>
     <t xml:space="preserve">2.76138782501221</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.40042209625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29213213920593</t>
+    <t xml:space="preserve">2.29213237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36432528495789</t>
+    <t xml:space="preserve">2.36432552337646</t>
   </si>
   <si>
     <t xml:space="preserve">2.59895324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3101806640625</t>
+    <t xml:space="preserve">2.31018042564392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32822871208191</t>
+    <t xml:space="preserve">2.32822895050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.65309810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01406383514404</t>
+    <t xml:space="preserve">3.01406359672546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19454646110535</t>
+    <t xml:space="preserve">3.19454669952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15844988822937</t>
+    <t xml:space="preserve">3.15845012664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.23064303398132</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">3.10430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17649841308594</t>
+    <t xml:space="preserve">3.17649817466736</t>
   </si>
   <si>
     <t xml:space="preserve">3.06820869445801</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">3.03211188316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97796726226807</t>
+    <t xml:space="preserve">2.97796702384949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92382216453552</t>
+    <t xml:space="preserve">2.9238224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94187068939209</t>
+    <t xml:space="preserve">2.94187045097351</t>
   </si>
   <si>
     <t xml:space="preserve">3.086256980896</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">2.90577411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9599187374115</t>
+    <t xml:space="preserve">2.95991897583008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74333930015564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7974841594696</t>
+    <t xml:space="preserve">2.79748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162925720215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23798751831055</t>
+    <t xml:space="preserve">2.23798727989197</t>
   </si>
   <si>
     <t xml:space="preserve">2.42749452590942</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">2.51773571968079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57188081741333</t>
+    <t xml:space="preserve">2.57188057899475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48163914680481</t>
+    <t xml:space="preserve">2.48163938522339</t>
   </si>
   <si>
     <t xml:space="preserve">2.49968767166138</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.55383229255676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44554257392883</t>
+    <t xml:space="preserve">2.44554281234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.6432785987854</t>
@@ -70205,6 +70205,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2633">
+      <c r="A2633" s="1" t="n">
+        <v>46156.2916666667</v>
+      </c>
+      <c r="B2633" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2633" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2633" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E2633" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="F2633" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2633" t="s">
+        <v>458</v>
+      </c>
+      <c r="H2633" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895930290222</v>
+        <v>2.24895906448364</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945937156677</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945937156677</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945937156677</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945937156677</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.09734392166138</v>
+        <v>2.0973436832428</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688184738159</v>
+        <v>2.36688208580017</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31634378433228</v>
+        <v>2.31634330749512</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745167732239</v>
+        <v>2.10745143890381</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472864151001</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472864151001</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.1782054901123</v>
+        <v>2.17820525169373</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G85" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G86" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G87" t="n">
-        <v>2.61429834365845</v>
+        <v>2.61429858207703</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664690971375</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664690971375</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664690971375</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.12791752815247</v>
+        <v>2.12791776657104</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.12791752815247</v>
+        <v>2.12791776657104</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.12791752815247</v>
+        <v>2.12791776657104</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.12791752815247</v>
+        <v>2.12791776657104</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G137" t="n">
-        <v>2.12791752815247</v>
+        <v>2.12791776657104</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G140" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G142" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.0410635471344</v>
+        <v>2.04106378555298</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078305244446</v>
+        <v>1.91078317165375</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420980453491</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693359375</v>
+        <v>1.85693383216858</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693359375</v>
+        <v>1.85693383216858</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G185" t="n">
-        <v>1.761394739151</v>
+        <v>1.76139461994171</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G186" t="n">
-        <v>1.761394739151</v>
+        <v>1.76139461994171</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G187" t="n">
-        <v>1.761394739151</v>
+        <v>1.76139461994171</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G190" t="n">
-        <v>2.21824550628662</v>
+        <v>2.21824526786804</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G202" t="n">
-        <v>2.57434606552124</v>
+        <v>2.57434582710266</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303117752075</v>
+        <v>2.58303141593933</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G210" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G211" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613018989563</v>
+        <v>2.53612995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706961631775</v>
+        <v>2.47706937789917</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669439315796</v>
+        <v>2.42669415473938</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G219" t="n">
-        <v>2.37110781669617</v>
+        <v>2.37110805511475</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425431251526</v>
+        <v>2.28425455093384</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.37110781669617</v>
+        <v>2.37110805511475</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G231" t="n">
-        <v>2.20087480545044</v>
+        <v>2.20087432861328</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.16265916824341</v>
+        <v>2.16265892982483</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G240" t="n">
-        <v>2.38674163818359</v>
+        <v>2.38674139976501</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G243" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.34505176544189</v>
+        <v>2.34505200386047</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.38153052330017</v>
+        <v>2.38153076171875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G257" t="n">
-        <v>2.3189959526062</v>
+        <v>2.31899571418762</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G262" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>2.25124979019165</v>
+        <v>2.25125002861023</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.32420706748962</v>
+        <v>2.32420682907104</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.33115553855896</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.33115553855896</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.33115553855896</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.33115553855896</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G272" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847899436951</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G276" t="n">
-        <v>2.6403546333313</v>
+        <v>2.64035487174988</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382886886597</v>
+        <v>2.64382863044739</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246697425842</v>
+        <v>2.69246673583984</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>2.61603569984436</v>
+        <v>2.61603593826294</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.6403546333313</v>
+        <v>2.64035487174988</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955718040466</v>
+        <v>2.57955694198608</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772557258606</v>
+        <v>2.65772533416748</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>2.77063536643982</v>
+        <v>2.7706356048584</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706711769104</v>
+        <v>2.84706664085388</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091586112976</v>
+        <v>2.90091609954834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110210418701</v>
+        <v>3.11110234260559</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044341087341</v>
+        <v>3.30044364929199</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.50889229774475</v>
+        <v>3.50889253616333</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020694732666</v>
+        <v>3.50020718574524</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124110221863</v>
+        <v>3.36124086380005</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.75</v>
       </c>
       <c r="G310" t="n">
-        <v>3.25701642036438</v>
+        <v>3.25701665878296</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>3.23964548110962</v>
+        <v>3.2396457195282</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>3.37861204147339</v>
+        <v>3.37861180305481</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34386992454529</v>
+        <v>3.34387040138245</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218029022217</v>
+        <v>3.30218076705933</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G333" t="n">
-        <v>3.47762537002563</v>
+        <v>3.47762513160706</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.7017080783844</v>
+        <v>3.70170783996582</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339771270752</v>
+        <v>3.7433979511261</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.7798764705658</v>
+        <v>3.77987670898438</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G339" t="n">
-        <v>3.78335070610046</v>
+        <v>3.78334999084473</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G340" t="n">
-        <v>3.78508734703064</v>
+        <v>3.78508710861206</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G342" t="n">
-        <v>4.03870010375977</v>
+        <v>4.03870058059692</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G343" t="n">
-        <v>4.03870010375977</v>
+        <v>4.03870058059692</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.0821270942688</v>
+        <v>4.08212757110596</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G345" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G355" t="n">
-        <v>4.39913463592529</v>
+        <v>4.39913415908813</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G356" t="n">
-        <v>4.65769863128662</v>
+        <v>4.65769910812378</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G361" t="n">
-        <v>4.34246301651001</v>
+        <v>4.34246253967285</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>4.29464626312256</v>
+        <v>4.2946457862854</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>4.10160827636719</v>
+        <v>4.10160875320435</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G399" t="n">
-        <v>4.10515022277832</v>
+        <v>4.10514974594116</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G401" t="n">
-        <v>4.16713428497314</v>
+        <v>4.1671347618103</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>4.17067670822144</v>
+        <v>4.17067718505859</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>4.17067670822144</v>
+        <v>4.17067718505859</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G422" t="n">
-        <v>3.94576096534729</v>
+        <v>3.94576120376587</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G446" t="n">
-        <v>4.37256956100464</v>
+        <v>4.3725700378418</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G448" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G456" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786762237549</v>
+        <v>4.20786714553833</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>4.29464626312256</v>
+        <v>4.2946457862854</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G481" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13525724411011</v>
+        <v>4.13525772094727</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.82533431053162</v>
+        <v>3.82533407211304</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G529" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G531" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G548" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.5</v>
       </c>
       <c r="G560" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G594" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G621" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>4.51601982116699</v>
+        <v>4.51601934432983</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G630" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G633" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G634" t="n">
-        <v>4.40976047515869</v>
+        <v>4.40975999832153</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G635" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G636" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G637" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G640" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G641" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G685" t="n">
-        <v>3.87846398353577</v>
+        <v>3.87846374511719</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G688" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G689" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>3.96701335906982</v>
+        <v>3.96701312065125</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.5</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G693" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G698" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G699" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G703" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G704" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G706" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G718" t="n">
-        <v>4.35663032531738</v>
+        <v>4.35663080215454</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.5</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.5</v>
       </c>
       <c r="G723" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.5</v>
       </c>
       <c r="G724" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G738" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G740" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G742" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G743" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G744" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G747" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G749" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G750" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G751" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G753" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.5</v>
       </c>
       <c r="G773" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.5</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G776" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>3.91388392448425</v>
+        <v>3.91388368606567</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G791" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G793" t="n">
-        <v>4.33892059326172</v>
+        <v>4.33892107009888</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.98472261428833</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G800" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G804" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G823" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G824" t="n">
-        <v>4.2680811882019</v>
+        <v>4.26808166503906</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G827" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G829" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G834" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.07327270507812</v>
+        <v>4.07327222824097</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G840" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G845" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -68986,6 +68986,32 @@
         <v>1.60000002384186</v>
       </c>
       <c r="H2639" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" s="1" t="n">
+        <v>46167.2916666667</v>
+      </c>
+      <c r="B2640" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2640" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D2640" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E2640" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F2640" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G2640" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H2640" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2742280960083</v>
+        <v>2.27422833442688</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22368955612183</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22368955612183</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2287437915802</v>
+        <v>2.22874355316162</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22368955612183</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18157410621643</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18157410621643</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18157410621643</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0973436832428</v>
+        <v>2.09734392166138</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522847175598</v>
+        <v>2.05522871017456</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401329994202</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688208580017</v>
+        <v>2.36688184738159</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053621292114</v>
+        <v>2.24053597450256</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G53" t="n">
-        <v>2.12429785728455</v>
+        <v>2.12429761886597</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831300735474</v>
+        <v>2.18831276893616</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G63" t="n">
-        <v>2.10745143890381</v>
+        <v>2.10745167732239</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820525169373</v>
+        <v>2.17820501327515</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G76" t="n">
-        <v>2.2742280960083</v>
+        <v>2.27422833442688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35845899581909</v>
+        <v>2.35845875740051</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G90" t="n">
-        <v>2.60387587547302</v>
+        <v>2.6038761138916</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>2.45796155929565</v>
+        <v>2.45796179771423</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45796155929565</v>
+        <v>2.45796179771423</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>2.45796155929565</v>
+        <v>2.45796179771423</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>2.45796155929565</v>
+        <v>2.45796179771423</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>2.45796155929565</v>
+        <v>2.45796179771423</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>2.1887149810791</v>
+        <v>2.18871521949768</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.5</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G135" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G137" t="n">
-        <v>2.12791776657104</v>
+        <v>2.12791752815247</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.5</v>
       </c>
       <c r="G138" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.5</v>
       </c>
       <c r="G139" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.5</v>
       </c>
       <c r="G144" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>2.10186147689819</v>
+        <v>2.10186123847961</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.10186147689819</v>
+        <v>2.10186123847961</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.0410635471344</v>
+        <v>2.04106378555298</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G148" t="n">
-        <v>2.03237819671631</v>
+        <v>2.03237843513489</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.03237819671631</v>
+        <v>2.03237843513489</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G150" t="n">
-        <v>2.03237819671631</v>
+        <v>2.03237843513489</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G151" t="n">
-        <v>2.03237819671631</v>
+        <v>2.03237843513489</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735606193542</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683922290802</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683922290802</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G166" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G167" t="n">
-        <v>1.85519659519196</v>
+        <v>1.85519647598267</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998571872711</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998571872711</v>
+        <v>1.84998548030853</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735606193542</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735606193542</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735606193542</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735606193542</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693347454071</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693347454071</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G191" t="n">
-        <v>2.31899571418762</v>
+        <v>2.3189959526062</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138878822327</v>
+        <v>2.50138854980469</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>2.43190574645996</v>
+        <v>2.43190550804138</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303141593933</v>
+        <v>2.58303117752075</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G210" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G211" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669439315796</v>
+        <v>2.42669463157654</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.43190574645996</v>
+        <v>2.43190550804138</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425455093384</v>
+        <v>2.28425431251526</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.51875948905945</v>
+        <v>2.51875972747803</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242294311523</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242294311523</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G253" t="n">
-        <v>2.31899571418762</v>
+        <v>2.3189959526062</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G257" t="n">
-        <v>2.31899571418762</v>
+        <v>2.3189959526062</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636689186096</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.30857348442078</v>
+        <v>2.3085732460022</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G262" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>2.25125002861023</v>
+        <v>2.25124979019165</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G272" t="n">
-        <v>2.32768130302429</v>
+        <v>2.32768106460571</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242294311523</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382886886597</v>
+        <v>2.64382863044739</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955694198608</v>
+        <v>2.57955718040466</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G291" t="n">
-        <v>2.77063536643982</v>
+        <v>2.7706356048584</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.74110507965088</v>
+        <v>2.7411048412323</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706711769104</v>
+        <v>2.84706664085388</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044317245483</v>
+        <v>3.30044341087341</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G309" t="n">
-        <v>3.13194727897644</v>
+        <v>3.13194704055786</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480982780457</v>
+        <v>3.28480958938599</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>3.32649946212769</v>
+        <v>3.32649922370911</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G327" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415113449097</v>
+        <v>3.47415089607239</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588777542114</v>
+        <v>3.47588801383972</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706068992615</v>
+        <v>3.58706116676331</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G339" t="n">
-        <v>3.78335070610046</v>
+        <v>3.78335046768188</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.0821270942688</v>
+        <v>4.08212757110596</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -69038,6 +69038,32 @@
         <v>1.62999999523163</v>
       </c>
       <c r="H2641" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" s="1" t="n">
+        <v>46169.2916666667</v>
+      </c>
+      <c r="B2642" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C2642" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="D2642" t="n">
+        <v>1.52999997138977</v>
+      </c>
+      <c r="E2642" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="F2642" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G2642" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="H2642" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G21" t="n">
-        <v>2.13945913314819</v>
+        <v>2.13945889472961</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.09734392166138</v>
+        <v>2.0973436832428</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688208580017</v>
+        <v>2.36688184738159</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3163435459137</v>
+        <v>2.31634378433228</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738215446472</v>
+        <v>2.25738191604614</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315149307251</v>
+        <v>2.17315125465393</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472816467285</v>
+        <v>2.16472840309143</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G90" t="n">
-        <v>2.60387587547302</v>
+        <v>2.6038761138916</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G111" t="n">
-        <v>2.51007413864136</v>
+        <v>2.51007437705994</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G120" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G121" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3971643447876</v>
+        <v>2.39716410636902</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078305244446</v>
+        <v>1.91078329086304</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683910369873</v>
+        <v>1.93683934211731</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G171" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G172" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>1.867356300354</v>
+        <v>1.86735618114471</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G174" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>1.85693383216858</v>
+        <v>1.85693371295929</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G183" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G184" t="n">
-        <v>1.75444614887238</v>
+        <v>1.75444626808167</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G190" t="n">
-        <v>2.21824550628662</v>
+        <v>2.21824526786804</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138878822327</v>
+        <v>2.50138902664185</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G197" t="n">
-        <v>2.32941794395447</v>
+        <v>2.32941818237305</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64904022216797</v>
+        <v>2.64903998374939</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G203" t="n">
-        <v>2.58303117752075</v>
+        <v>2.58303141593933</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G204" t="n">
-        <v>2.58650541305542</v>
+        <v>2.58650517463684</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401761054993</v>
+        <v>2.48401784896851</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162525177002</v>
+        <v>2.30162501335144</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242270469666</v>
+        <v>2.36242246627808</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847875595093</v>
+        <v>2.38847851753235</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087159156799</v>
+        <v>2.57087182998657</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772533416748</v>
+        <v>2.65772557258606</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.74110507965088</v>
+        <v>2.7411048412323</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G293" t="n">
-        <v>2.80537724494934</v>
+        <v>2.80537700653076</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G294" t="n">
-        <v>2.84706687927246</v>
+        <v>2.84706664085388</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G295" t="n">
-        <v>2.90091633796692</v>
+        <v>2.90091609954834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110234260559</v>
+        <v>3.11110210418701</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.50889229774475</v>
+        <v>3.50889253616333</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020718574524</v>
+        <v>3.50020694732666</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4654655456543</v>
+        <v>3.46546530723572</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G305" t="n">
-        <v>3.21185255050659</v>
+        <v>3.21185278892517</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.75</v>
       </c>
       <c r="G310" t="n">
-        <v>3.25701642036438</v>
+        <v>3.25701665878296</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480982780457</v>
+        <v>3.28480958938599</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>3.30218052864075</v>
+        <v>3.30218076705933</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170783996582</v>
+        <v>3.70170760154724</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339771270752</v>
+        <v>3.7433979511261</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987694740295</v>
+        <v>3.7798764705658</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -69090,6 +69090,32 @@
         <v>1.58000004291534</v>
       </c>
       <c r="H2643" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" s="1" t="n">
+        <v>46171.2916666667</v>
+      </c>
+      <c r="B2644" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C2644" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D2644" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="E2644" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F2644" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="G2644" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="H2644" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24895930290222</v>
+        <v>2.24895906448364</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2287437915802</v>
+        <v>2.22874355316162</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22369003295898</v>
+        <v>2.22368979454041</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18157458305359</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18157458305359</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18157458305359</v>
+        <v>2.18157434463501</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0973436832428</v>
+        <v>2.09734392166138</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522871017456</v>
+        <v>2.05522847175598</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684361457825</v>
+        <v>2.20684337615967</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401306152344</v>
+        <v>2.25401282310486</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688184738159</v>
+        <v>2.36688232421875</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31634378433228</v>
+        <v>2.3163435459137</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053597450256</v>
+        <v>2.24053621292114</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103604316711</v>
+        <v>2.13103628158569</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630531311035</v>
+        <v>2.15630555152893</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831300735474</v>
+        <v>2.18831324577332</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576701164246</v>
+        <v>2.10576677322388</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16472840309143</v>
+        <v>2.16472816467285</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.27085900306702</v>
+        <v>2.2708592414856</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>2.35845875740051</v>
+        <v>2.35845899581909</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692788124084</v>
+        <v>2.59692811965942</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>2.5621862411499</v>
+        <v>2.56218647956848</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>2.46664714813232</v>
+        <v>2.4666473865509</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.5</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.5</v>
       </c>
       <c r="G138" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.5</v>
       </c>
       <c r="G139" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.5</v>
       </c>
       <c r="G144" t="n">
-        <v>2.1713445186615</v>
+        <v>2.17134428024292</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G145" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.10186123847961</v>
+        <v>2.10186147689819</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>2.0410635471344</v>
+        <v>2.04106378555298</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.95421016216278</v>
+        <v>1.9542099237442</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G165" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G166" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G167" t="n">
-        <v>1.85519647598267</v>
+        <v>1.85519659519196</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G177" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.78050231933594</v>
+        <v>1.78050243854523</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138878822327</v>
+        <v>2.50138902664185</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800904273987</v>
+        <v>2.41800880432129</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G209" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G210" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G211" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613042831421</v>
+        <v>2.53613018989563</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G220" t="n">
-        <v>2.28425407409668</v>
+        <v>2.28425431251526</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G225" t="n">
-        <v>2.51875972747803</v>
+        <v>2.51875948905945</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331488609314</v>
+        <v>2.34331464767456</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G231" t="n">
-        <v>2.20087456703186</v>
+        <v>2.20087432861328</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G235" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29988813400269</v>
+        <v>2.29988789558411</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G247" t="n">
-        <v>2.3502631187439</v>
+        <v>2.35026335716248</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.33636665344238</v>
+        <v>2.3363664150238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.33115530014038</v>
+        <v>2.3311550617218</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246697425842</v>
+        <v>2.69246673583984</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955718040466</v>
+        <v>2.57955694198608</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G287" t="n">
-        <v>2.68378138542175</v>
+        <v>2.68378162384033</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020718574524</v>
+        <v>3.50020694732666</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G305" t="n">
-        <v>3.21185255050659</v>
+        <v>3.21185278892517</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G309" t="n">
-        <v>3.13194680213928</v>
+        <v>3.13194704055786</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>3.34386992454529</v>
+        <v>3.34387016296387</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588801383972</v>
+        <v>3.47588777542114</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.58706116676331</v>
+        <v>3.58706092834473</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>3.56100463867188</v>
+        <v>3.56100487709045</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.74339747428894</v>
+        <v>3.7433979511261</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.77987599372864</v>
+        <v>3.7798764705658</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G341" t="n">
-        <v>3.90668249130249</v>
+        <v>3.90668296813965</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.0821270942688</v>
+        <v>4.08212757110596</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G356" t="n">
-        <v>4.65769863128662</v>
+        <v>4.65769910812378</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G360" t="n">
-        <v>4.44517946243286</v>
+        <v>4.44517993927002</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G368" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G369" t="n">
-        <v>4.42392826080322</v>
+        <v>4.42392778396606</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>4.10160827636719</v>
+        <v>4.10160875320435</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G388" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G389" t="n">
-        <v>4.19547033309937</v>
+        <v>4.19547080993652</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G392" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G393" t="n">
-        <v>4.23797464370728</v>
+        <v>4.23797416687012</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G394" t="n">
-        <v>4.39027976989746</v>
+        <v>4.3902792930603</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G395" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G396" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G398" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G399" t="n">
-        <v>4.10515022277832</v>
+        <v>4.10514974594116</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G400" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G406" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G408" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G413" t="n">
-        <v>4.04316520690918</v>
+        <v>4.04316568374634</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G434" t="n">
-        <v>4.11754703521729</v>
+        <v>4.11754751205444</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09983777999878</v>
+        <v>4.09983730316162</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G444" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5</v>
       </c>
       <c r="G447" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5</v>
       </c>
       <c r="G451" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5</v>
       </c>
       <c r="G452" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5</v>
       </c>
       <c r="G453" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>4.27693605422974</v>
+        <v>4.27693557739258</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G455" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786762237549</v>
+        <v>4.20786714553833</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G466" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G467" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G469" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G470" t="n">
-        <v>4.14942502975464</v>
+        <v>4.14942455291748</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G479" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G481" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G483" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G484" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G485" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G486" t="n">
-        <v>4.07858562469482</v>
+        <v>4.07858514785767</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13525724411011</v>
+        <v>4.13525772094727</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G495" t="n">
-        <v>4.15296745300293</v>
+        <v>4.15296697616577</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G499" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G502" t="n">
-        <v>3.95107436180115</v>
+        <v>3.95107388496399</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G504" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.8253345489502</v>
+        <v>3.82533407211304</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.02899837493896</v>
+        <v>4.02899789810181</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G517" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G519" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G524" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G538" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G541" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G542" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5</v>
       </c>
       <c r="G549" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G559" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.5</v>
       </c>
       <c r="G560" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>4.0555624961853</v>
+        <v>4.05556201934814</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G567" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G568" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5</v>
       </c>
       <c r="G579" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G595" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5</v>
       </c>
       <c r="G600" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5</v>
       </c>
       <c r="G601" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5</v>
       </c>
       <c r="G605" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G606" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G608" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G609" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G610" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G611" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G612" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G613" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G615" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G621" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5</v>
       </c>
       <c r="G623" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5</v>
       </c>
       <c r="G624" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5</v>
       </c>
       <c r="G627" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5</v>
       </c>
       <c r="G628" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5</v>
       </c>
       <c r="G629" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G640" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G641" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G651" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G652" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G656" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G657" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G660" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G662" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G664" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G665" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G667" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G668" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G684" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.5</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G693" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5</v>
       </c>
       <c r="G696" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G709" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G710" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G711" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G712" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5</v>
       </c>
       <c r="G714" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5</v>
       </c>
       <c r="G715" t="n">
-        <v>4.42747020721436</v>
+        <v>4.4274697303772</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G719" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.5</v>
       </c>
       <c r="G722" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.5</v>
       </c>
       <c r="G723" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.5</v>
       </c>
       <c r="G724" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G733" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G754" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G755" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G756" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G757" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G758" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G759" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G760" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G761" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G762" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G763" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G764" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G765" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G767" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G768" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G772" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.5</v>
       </c>
       <c r="G773" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G774" t="n">
-        <v>4.00243282318115</v>
+        <v>4.00243330001831</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>4.5</v>
       </c>
       <c r="G775" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G781" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G782" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G783" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G794" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G795" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G798" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.98472332954407</v>
+        <v>3.98472285270691</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G801" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.28579092025757</v>
+        <v>4.28579139709473</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>4.16182136535645</v>
+        <v>4.1618218421936</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G830" t="n">
-        <v>4.03785228729248</v>
+        <v>4.03785276412964</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G831" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G832" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G833" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G837" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G838" t="n">
-        <v>4.09098196029663</v>
+        <v>4.09098243713379</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G840" t="n">
-        <v>4.23266172409058</v>
+        <v>4.23266124725342</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G841" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G842" t="n">
-        <v>4.10869216918945</v>
+        <v>4.10869169235229</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G843" t="n">
-        <v>4.19724178314209</v>
+        <v>4.19724130630493</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G845" t="n">
-        <v>4.21495151519775</v>
+        <v>4.21495199203491</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -69168,6 +69168,32 @@
         <v>1.55999994277954</v>
       </c>
       <c r="H2646" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" s="1" t="n">
+        <v>46176.2916666667</v>
+      </c>
+      <c r="B2647" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2647" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D2647" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="E2647" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="F2647" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G2647" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="H2647" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LFG.MI.xlsx
+++ b/data/LFG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>2.23211288452148</v>
+        <v>2.23211312294006</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18157434463501</v>
+        <v>2.18157458305359</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05522847175598</v>
+        <v>2.05522871017456</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.20684337615967</v>
+        <v>2.20684361457825</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.25401282310486</v>
+        <v>2.25401306152344</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.36688232421875</v>
+        <v>2.36688208580017</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.75</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3163435459137</v>
+        <v>2.31634330749512</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G39" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G40" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>2.25738191604614</v>
+        <v>2.25738215446472</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G42" t="n">
-        <v>2.24053621292114</v>
+        <v>2.24053597450256</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G43" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G44" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G46" t="n">
-        <v>2.17315125465393</v>
+        <v>2.17315149307251</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12261295318604</v>
+        <v>2.12261319160461</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G50" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G53" t="n">
-        <v>2.12429761886597</v>
+        <v>2.12429785728455</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G54" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G55" t="n">
-        <v>2.11418986320496</v>
+        <v>2.11419010162354</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G56" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G59" t="n">
-        <v>2.13103628158569</v>
+        <v>2.13103604316711</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G60" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>2.15630555152893</v>
+        <v>2.15630531311035</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G62" t="n">
-        <v>2.18831324577332</v>
+        <v>2.18831300735474</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>2.10576677322388</v>
+        <v>2.1057665348053</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>2.14788222312927</v>
+        <v>2.14788246154785</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>2.14788222312927</v>
+        <v>2.14788246154785</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G75" t="n">
-        <v>2.17820501327515</v>
+        <v>2.1782054901123</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.2708592414856</v>
+        <v>2.27085900306702</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G82" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59692811965942</v>
+        <v>2.59692788124084</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G92" t="n">
-        <v>2.59692811965942</v>
+        <v>2.59692788124084</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>2.59692811965942</v>
+        <v>2.59692788124084</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G111" t="n">
-        <v>2.51007437705994</v>
+        <v>2.51007413864136</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G116" t="n">
-        <v>2.45796179771423</v>
+        <v>2.45796155929565</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G125" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G127" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G128" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G129" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G130" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>2.1887149810791</v>
+        <v>2.18871521949768</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G140" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G141" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G142" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.91078329086304</v>
+        <v>1.91078305244446</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.25</v>
       </c>
       <c r="G154" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.25</v>
       </c>
       <c r="G155" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.25</v>
       </c>
       <c r="G156" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.25</v>
       </c>
       <c r="G157" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.25</v>
       </c>
       <c r="G158" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.93683934211731</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.93683934211731</v>
+        <v>1.93683922290802</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.25</v>
       </c>
       <c r="G161" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1.9542099237442</v>
+        <v>1.95420968532562</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>1.84129989147186</v>
+        <v>1.84129977226257</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>1.84998548030853</v>
+        <v>1.84998559951782</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G177" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G178" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.78050243854523</v>
+        <v>1.78050231933594</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G193" t="n">
-        <v>2.50138902664185</v>
+        <v>2.50138878822327</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.75</v>
       </c>
       <c r="G196" t="n">
-        <v>2.38847851753235</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G199" t="n">
-        <v>2.64903998374939</v>
+        <v>2.64904022216797</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G207" t="n">
-        <v>2.41800880432129</v>
+        <v>2.41800904273987</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>2.53613018989563</v>
+        <v>2.53612995147705</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G214" t="n">
-        <v>2.48401784896851</v>
+        <v>2.48401761054993</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G215" t="n">
-        <v>2.47706961631775</v>
+        <v>2.47706937789917</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G216" t="n">
-        <v>2.42669439315796</v>
+        <v>2.42669415473938</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G222" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G223" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G227" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G228" t="n">
-        <v>2.34331464767456</v>
+        <v>2.34331488609314</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.75</v>
       </c>
       <c r="G229" t="n">
-        <v>2.38847851753235</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G230" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>2.21477127075195</v>
+        <v>2.21477150917053</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>2.16265892982483</v>
+        <v>2.16265916824341</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G234" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G235" t="n">
-        <v>2.29988789558411</v>
+        <v>2.29988813400269</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29988789558411</v>
+        <v>2.29988813400269</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.75</v>
       </c>
       <c r="G237" t="n">
-        <v>2.38847851753235</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G238" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G240" t="n">
-        <v>2.38674139976501</v>
+        <v>2.38674163818359</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.75</v>
       </c>
       <c r="G244" t="n">
-        <v>2.38847851753235</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G246" t="n">
-        <v>2.3363664150238</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G247" t="n">
-        <v>2.35026335716248</v>
+        <v>2.3502631187439</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>2.33462953567505</v>
+        <v>2.33462929725647</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G255" t="n">
-        <v>2.38153076171875</v>
+        <v>2.38153100013733</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G258" t="n">
-        <v>2.3363664150238</v>
+        <v>2.33636665344238</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G259" t="n">
-        <v>2.31031060218811</v>
+        <v>2.31031036376953</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G260" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G261" t="n">
-        <v>2.3085732460022</v>
+        <v>2.30857348442078</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G262" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>2.30162501335144</v>
+        <v>2.30162525177002</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G268" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G269" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G270" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G271" t="n">
-        <v>2.3311550617218</v>
+        <v>2.33115530014038</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G272" t="n">
-        <v>2.32768106460571</v>
+        <v>2.32768130302429</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.36242246627808</v>
+        <v>2.36242270469666</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>2.38847851753235</v>
+        <v>2.38847875595093</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G276" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G277" t="n">
-        <v>2.64382886886597</v>
+        <v>2.64382863044739</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>2.69246673583984</v>
+        <v>2.69246697425842</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>2.57087182998657</v>
+        <v>2.57087135314941</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>2.64035487174988</v>
+        <v>2.6403546333313</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>2.57955694198608</v>
+        <v>2.57955718040466</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>2.65772557258606</v>
+        <v>2.65772533416748</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G292" t="n">
-        <v>2.7411048412323</v>
+        <v>2.74110507965088</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G296" t="n">
-        <v>3.11110210418701</v>
+        <v>3.11110234260559</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G297" t="n">
-        <v>3.30044341087341</v>
+        <v>3.30044364929199</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>3.46546530723572</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G300" t="n">
-        <v>3.50020694732666</v>
+        <v>3.50020718574524</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>3.46546530723572</v>
+        <v>3.4654655456543</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.36124110221863</v>
+        <v>3.36124086380005</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G303" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G305" t="n">
-        <v>3.21185278892517</v>
+        <v>3.21185255050659</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G307" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G308" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G311" t="n">
-        <v>3.23096060752869</v>
+        <v>3.23096036911011</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G314" t="n">
-        <v>3.21358966827393</v>
+        <v>3.21358942985535</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>3.17016267776489</v>
+        <v>3.17016291618347</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G317" t="n">
-        <v>3.29175806045532</v>
+        <v>3.29175782203674</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G319" t="n">
-        <v>3.28480958938599</v>
+        <v>3.28480982780457</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4</v>
       </c>
       <c r="G322" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="G323" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G326" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G327" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G329" t="n">
-        <v>3.43072414398193</v>
+        <v>3.43072390556335</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4</v>
       </c>
       <c r="G330" t="n">
-        <v>3.47415089607239</v>
+        <v>3.47415113449097</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G331" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G332" t="n">
-        <v>3.47588777542114</v>
+        <v>3.47588801383972</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>3.56100487709045</v>
+        <v>3.56100463867188</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>3.70170760154724</v>
+        <v>3.70170783996582</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G337" t="n">
-        <v>3.7433979511261</v>
+        <v>3.74339771270752</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G338" t="n">
-        <v>3.7798764705658</v>
+        <v>3.77987670898438</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G341" t="n">
-        <v>3.90668296813965</v>
+        <v>3.90668272972107</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G345" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G355" t="n">
-        <v>4.39913415908813</v>
+        <v>4.39913463592529</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G356" t="n">
-        <v>4.65769910812378</v>
+        <v>4.65769863128662</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G361" t="n">
-        <v>4.34246253967285</v>
+        <v>4.34246301651001</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G372" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G373" t="n">
-        <v>4.10160875320435</v>
+        <v>4.10160827636719</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G391" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G399" t="n">
-        <v>4.10514974594116</v>
+        <v>4.10515022277832</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G401" t="n">
-        <v>4.1671347618103</v>
+        <v>4.16713428497314</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>4.17067718505859</v>
+        <v>4.17067670822144</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G422" t="n">
-        <v>3.94576120376587</v>
+        <v>3.94576096534729</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.5</v>
       </c>
       <c r="G423" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G446" t="n">
-        <v>4.3725700378418</v>
+        <v>4.37256956100464</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G448" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G456" t="n">
-        <v>4.33892107009888</v>
+        <v>4.33892059326172</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G459" t="n">
-        <v>4.23266124725342</v>
+        <v>4.23266172409058</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G464" t="n">
-        <v>4.20786714553833</v>
+        <v>4.20786762237549</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G471" t="n">
-        <v>4.2946457862854</v>
+        <v>4.29464626312256</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G472" t="n">
-        <v>4.35663080215454</v>
+        <v>4.35663032531738</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G481" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G482" t="n">
-        <v>4.21495199203491</v>
+        <v>4.21495151519775</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>4.13525772094727</v>
+        <v>4.13525724411011</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G506" t="n">
-        <v>3.82533407211304</v>
+        <v>3.82533431053162</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G514" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.5</v>
       </c>
       <c r="G521" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>3.91388368606567</v>
+        <v>3.91388392448425</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G529" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G531" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G533" t="n">
-        <v>3.96701312065125</v>
+        <v>3.96701335906982</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.5</v>
       </c>
       <c r="G534" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.5</v>
       </c>
       <c r="G536" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.5</v>
       </c>
       <c r="G539" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.07327222824097</v>
+        <v>4.07327270507812</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.5</v>
       </c>
       <c r="G543" t="n">
-        <v>3.98472285270691</v>
+        <v>3.98472261428833</v>
       <